--- a/Perú V.1.xlsx
+++ b/Perú V.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CELSO HOJAS DE RUTA\RADIOAYUDAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CELSO HOJAS DE RUTA\FRECUENCIAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F684AA1-719F-4139-B1EB-66574D355B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07A5CBE-3FBD-44B6-9F93-E6E680E70EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{461DCE75-370B-4E44-A060-84CF19771C02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="597" xr2:uid="{461DCE75-370B-4E44-A060-84CF19771C02}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -43,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="418">
   <si>
     <t>Country</t>
   </si>
@@ -711,18 +709,12 @@
     <t>SPHO</t>
   </si>
   <si>
-    <t>13º09’17.41” S</t>
-  </si>
-  <si>
     <t>074º12’15.90” W</t>
   </si>
   <si>
     <t>SPJC</t>
   </si>
   <si>
-    <t>12º01’18.79”S</t>
-  </si>
-  <si>
     <t>077°06’51.54”W</t>
   </si>
   <si>
@@ -738,9 +730,6 @@
     <t>SPJL</t>
   </si>
   <si>
-    <t>15°28’00.69”S</t>
-  </si>
-  <si>
     <t>070°09’28.38”W</t>
   </si>
   <si>
@@ -756,18 +745,12 @@
     <t>SPZA</t>
   </si>
   <si>
-    <t>14°51’14.90”S</t>
-  </si>
-  <si>
     <t>074°57’42.38”W</t>
   </si>
   <si>
     <t>SPZO</t>
   </si>
   <si>
-    <t>13°32'08.60'”S</t>
-  </si>
-  <si>
     <t>071°56'19.61'”W</t>
   </si>
   <si>
@@ -792,18 +775,12 @@
     <t>SPMF</t>
   </si>
   <si>
-    <t>11º19’31.86” S</t>
-  </si>
-  <si>
     <t>074º32’08.98” W</t>
   </si>
   <si>
     <t>SPSO</t>
   </si>
   <si>
-    <t>13°44’41.28”S</t>
-  </si>
-  <si>
     <t>076°13’13.48”W</t>
   </si>
   <si>
@@ -819,9 +796,6 @@
     <t>SPTN</t>
   </si>
   <si>
-    <t>18°03'11.84''S</t>
-  </si>
-  <si>
     <t>070°16'32.96''W</t>
   </si>
   <si>
@@ -849,9 +823,6 @@
     <t>SPTU</t>
   </si>
   <si>
-    <t>12º36’49.79” S</t>
-  </si>
-  <si>
     <t>069º13’43.24” W</t>
   </si>
   <si>
@@ -867,9 +838,6 @@
     <t>SPQU</t>
   </si>
   <si>
-    <t>16°20’26.08”S</t>
-  </si>
-  <si>
     <t>071°34’14.89”W</t>
   </si>
   <si>
@@ -915,9 +883,6 @@
     <t>SPLO</t>
   </si>
   <si>
-    <t>17°41’42.10”S</t>
-  </si>
-  <si>
     <t>071°20’38.15”W</t>
   </si>
   <si>
@@ -942,9 +907,6 @@
     <t>SPAY</t>
   </si>
   <si>
-    <t>10º43’43” S</t>
-  </si>
-  <si>
     <t>073º45’58” W</t>
   </si>
   <si>
@@ -961,9 +923,6 @@
   </si>
   <si>
     <t>SPJJ</t>
-  </si>
-  <si>
-    <t>11º47’0.20” S</t>
   </si>
   <si>
     <t>075º28’24.10” W</t>
@@ -1172,6 +1131,195 @@
   </si>
   <si>
     <t>NEWLIMA RESERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08° 5'7.36"S</t>
+  </si>
+  <si>
+    <t>VHF - AA MAIN</t>
+  </si>
+  <si>
+    <t>079° 6'28.47"W</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 119.500 MHz</t>
+  </si>
+  <si>
+    <t>VHF -  AA/ALTERNA DE 135.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  07° 8'35.91"S</t>
+  </si>
+  <si>
+    <t>VHF - AA/ ALTERNA DE 128.100</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 128.100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  05°12'21.96"S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 013°21'22.19"S</t>
+  </si>
+  <si>
+    <t>016°20’26.08”S</t>
+  </si>
+  <si>
+    <t>010º43’43” S</t>
+  </si>
+  <si>
+    <t>013º09’17.41” S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 074°11'28.47"W</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 128.500</t>
+  </si>
+  <si>
+    <t>013°32'08.60'”S</t>
+  </si>
+  <si>
+    <t>017°41’42.10”S</t>
+  </si>
+  <si>
+    <t>011º47’0.20” S</t>
+  </si>
+  <si>
+    <t>015°28’00.69”S</t>
+  </si>
+  <si>
+    <t>011º19’31.86” S</t>
+  </si>
+  <si>
+    <t>014°51’14.90”S</t>
+  </si>
+  <si>
+    <t>013°44’41.28”S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 080°37'5.65"W</t>
+  </si>
+  <si>
+    <t>013°44'18.13"S</t>
+  </si>
+  <si>
+    <t>012º36’49.79” S</t>
+  </si>
+  <si>
+    <t>018°03'11.84''S</t>
+  </si>
+  <si>
+    <t>012º01’18.79”S</t>
+  </si>
+  <si>
+    <t>076°13'18.07"W</t>
+  </si>
+  <si>
+    <t>078°37'33.77"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 078°37'33.77"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 76°15'6.77"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 010°41'46.53"S</t>
+  </si>
+  <si>
+    <t>VHF -  AA MAIN</t>
+  </si>
+  <si>
+    <t>VHF - AA/ ALTERNA DE 128.500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  03°47'8.93"S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 73°18'13.53"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  08°23'7.67"S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 074°34'25.56"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 072° 8'7.25"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 016°22'25.06"S</t>
+  </si>
+  <si>
+    <t>016°32'9.63"S</t>
+  </si>
+  <si>
+    <t>072°36'25.61"W</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNO DE 128.800</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 128.800</t>
+  </si>
+  <si>
+    <t>069°13'28.05"W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 012°36'7.96"S</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>NORTE (NOR-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VHF - AA/ALTERNA DE 128.100 </t>
+  </si>
+  <si>
+    <t>ORIENTE</t>
+  </si>
+  <si>
+    <t>SUR-2</t>
+  </si>
+  <si>
+    <t>RADAR SUR (SUR-2)</t>
+  </si>
+  <si>
+    <t>ACOPIA GRANDE / CUSCO</t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 124.750</t>
+  </si>
+  <si>
+    <t>071°37′36.4″ W</t>
+  </si>
+  <si>
+    <t>013°36′26.1″S</t>
+  </si>
+  <si>
+    <t>RADAR SUR (SUR-1)</t>
+  </si>
+  <si>
+    <t>RADAR NORTE (NOR-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJAMARCA / CERRO COLPAYOJ  </t>
+  </si>
+  <si>
+    <t>PASCO / CERRO DE PASCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREQUIPA / CERRO RAYADO </t>
+  </si>
+  <si>
+    <t>AYACUCHO / CERRO TOCCTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREQUIPA / SIHUAS </t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1332,7 @@
     <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1230,6 +1378,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1251,7 +1405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1320,9 +1474,6 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1341,6 +1492,52 @@
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1841,10 +2038,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6ED1388A-2980-4ECD-AD44-762A31FCE264}" name="Table1" displayName="Table1" ref="A1:Q116" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q116" xr:uid="{6ED1388A-2980-4ECD-AD44-762A31FCE264}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q116">
-    <sortCondition ref="F1:F116"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6ED1388A-2980-4ECD-AD44-762A31FCE264}" name="Table1" displayName="Table1" ref="A1:Q160" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q160" xr:uid="{6ED1388A-2980-4ECD-AD44-762A31FCE264}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q160">
+    <sortCondition ref="D1:D160"/>
   </sortState>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{49C92713-ECDF-4A9D-85E9-5FE8128DA9D5}" name="ICAO Regional Office" dataDxfId="16"/>
@@ -2186,19 +2383,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91B314B-F5DE-42A9-AA04-08E465D3B17B}">
-  <dimension ref="A1:R116"/>
+  <dimension ref="A1:R160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="66.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13" style="3" customWidth="1"/>
+    <col min="4" max="4" width="56.875" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.125" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="37.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="17.125" style="3" customWidth="1"/>
     <col min="11" max="11" width="13.875" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.125" style="3" customWidth="1"/>
     <col min="13" max="13" width="12.125" style="6" customWidth="1"/>
@@ -2277,33 +2474,33 @@
       <c r="C2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>285</v>
+      <c r="D2" s="42" t="s">
+        <v>407</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="H2" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="9" t="s">
-        <v>312</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="H2" s="45">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I2" s="43"/>
+      <c r="J2" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="K2" s="38"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2"/>
     </row>
@@ -2317,34 +2514,34 @@
       <c r="C3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>285</v>
+      <c r="D3" s="42" t="s">
+        <v>407</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="H3" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q3" s="20"/>
+        <v>235</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="H3" s="45">
+        <v>124.75</v>
+      </c>
+      <c r="I3" s="43"/>
+      <c r="J3" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="K3" s="38"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
       <c r="R3"/>
     </row>
     <row r="4" spans="1:18">
@@ -2357,34 +2554,34 @@
       <c r="C4" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>314</v>
+      <c r="D4" s="22" t="s">
+        <v>275</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="H4" s="25">
-        <v>118.3</v>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q4" s="20"/>
+        <v>276</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="H4" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q4" s="9"/>
       <c r="R4"/>
     </row>
     <row r="5" spans="1:18">
@@ -2397,32 +2594,32 @@
       <c r="C5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>314</v>
+      <c r="D5" s="22" t="s">
+        <v>275</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="H5" s="25">
+        <v>276</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="H5" s="24">
         <v>121.5</v>
       </c>
-      <c r="I5" s="30"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q5" s="20"/>
     </row>
@@ -2436,30 +2633,32 @@
       <c r="C6" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>314</v>
+      <c r="D6" s="28" t="s">
+        <v>301</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="21">
-        <v>126.9</v>
-      </c>
-      <c r="I6" s="30"/>
+        <v>240</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="H6" s="24">
+        <v>118.3</v>
+      </c>
+      <c r="I6" s="29"/>
       <c r="J6" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
+        <v>125</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
       <c r="N6" s="20"/>
-      <c r="O6" s="20" t="s">
-        <v>341</v>
-      </c>
+      <c r="O6" s="20"/>
       <c r="P6" s="20" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="Q6" s="20"/>
       <c r="R6"/>
@@ -2474,32 +2673,32 @@
       <c r="C7" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="H7" s="21">
-        <v>118.7</v>
-      </c>
-      <c r="I7" s="30"/>
+      <c r="D7" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="H7" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I7" s="29"/>
       <c r="J7" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="20"/>
+        <v>300</v>
+      </c>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
       <c r="N7" s="20"/>
       <c r="O7" s="20"/>
       <c r="P7" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q7" s="20"/>
       <c r="R7"/>
@@ -2514,32 +2713,34 @@
       <c r="C8" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="H8" s="28">
-        <v>121.9</v>
-      </c>
-      <c r="I8" s="30"/>
+      <c r="D8" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="H8" s="21">
+        <v>126.9</v>
+      </c>
+      <c r="I8" s="29"/>
       <c r="J8" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
+        <v>289</v>
+      </c>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
       <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
+      <c r="O8" s="20" t="s">
+        <v>328</v>
+      </c>
       <c r="P8" s="20" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="Q8" s="20"/>
     </row>
@@ -2553,32 +2754,34 @@
       <c r="C9" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="H9" s="28">
-        <v>121.5</v>
-      </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="20"/>
+      <c r="D9" s="29" t="s">
+        <v>415</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="H9" s="21">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="J9" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K9" s="29"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P9" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q9" s="20"/>
     </row>
@@ -2592,36 +2795,38 @@
       <c r="C10" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>275</v>
+      <c r="D10" s="29" t="s">
+        <v>415</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>396</v>
       </c>
       <c r="H10" s="21">
-        <v>130.9</v>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K10" s="30"/>
+        <v>124.75</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K10" s="29"/>
       <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
+      <c r="M10" s="29"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>397</v>
+      </c>
       <c r="P10" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q10" s="20"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" s="37" customFormat="1">
       <c r="A11" s="22" t="s">
         <v>40</v>
       </c>
@@ -2631,37 +2836,38 @@
       <c r="C11" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="H11" s="28">
-        <v>126.9</v>
-      </c>
-      <c r="I11" s="27"/>
-      <c r="J11" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K11" s="30"/>
+      <c r="D11" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="H11" s="21">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K11" s="29"/>
       <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
+      <c r="M11" s="29"/>
       <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P11" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q11" s="20"/>
-      <c r="R11"/>
-    </row>
-    <row r="12" spans="1:18">
+    </row>
+    <row r="12" spans="1:18" s="37" customFormat="1">
       <c r="A12" s="22" t="s">
         <v>40</v>
       </c>
@@ -2671,39 +2877,38 @@
       <c r="C12" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>300</v>
+      <c r="D12" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>393</v>
       </c>
       <c r="H12" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I12" s="27"/>
-      <c r="J12" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K12" s="30"/>
+        <v>124.75</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K12" s="29"/>
       <c r="L12" s="30"/>
-      <c r="M12" s="20"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20" t="s">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q12" s="20"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:18">
+    </row>
+    <row r="13" spans="1:18" s="37" customFormat="1">
       <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
@@ -2713,37 +2918,36 @@
       <c r="C13" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>223</v>
+      <c r="D13" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>265</v>
       </c>
       <c r="H13" s="21">
-        <v>126.9</v>
-      </c>
-      <c r="I13" s="30"/>
+        <v>118.7</v>
+      </c>
+      <c r="I13" s="29"/>
       <c r="J13" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
+        <v>46</v>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="20"/>
       <c r="N13" s="20"/>
       <c r="O13" s="20"/>
       <c r="P13" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q13" s="20"/>
-      <c r="R13"/>
-    </row>
-    <row r="14" spans="1:18">
+    </row>
+    <row r="14" spans="1:18" s="37" customFormat="1">
       <c r="A14" s="22" t="s">
         <v>40</v>
       </c>
@@ -2753,35 +2957,34 @@
       <c r="C14" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="H14" s="21">
-        <v>118.1</v>
-      </c>
-      <c r="I14" s="30"/>
+      <c r="D14" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="H14" s="27">
+        <v>121.9</v>
+      </c>
+      <c r="I14" s="29"/>
       <c r="J14" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="20"/>
+        <v>255</v>
+      </c>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
       <c r="N14" s="20"/>
       <c r="O14" s="20"/>
       <c r="P14" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q14" s="20"/>
-      <c r="R14"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="22" t="s">
@@ -2793,34 +2996,32 @@
       <c r="C15" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="H15" s="25">
+      <c r="D15" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="H15" s="27">
         <v>121.5</v>
       </c>
-      <c r="I15" s="30"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K15" s="30"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="20" t="s">
-        <v>319</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="20"/>
       <c r="P15" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q15" s="20"/>
       <c r="R15"/>
@@ -2835,32 +3036,32 @@
       <c r="C16" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="H16" s="25">
-        <v>120.1</v>
-      </c>
-      <c r="I16" s="30"/>
+      <c r="D16" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="H16" s="21">
+        <v>130.9</v>
+      </c>
+      <c r="I16" s="29"/>
       <c r="J16" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
       <c r="P16" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q16" s="20"/>
       <c r="R16"/>
@@ -2876,31 +3077,31 @@
         <v>42</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="H17" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K17" s="30"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
+        <v>287</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="H17" s="27">
+        <v>126.9</v>
+      </c>
+      <c r="I17" s="26"/>
+      <c r="J17" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="20"/>
       <c r="O17" s="20"/>
       <c r="P17" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q17" s="20"/>
       <c r="R17"/>
@@ -2916,31 +3117,33 @@
         <v>42</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>106</v>
+        <v>305</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="H18" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I18" s="30"/>
+        <v>287</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="H18" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I18" s="26"/>
       <c r="J18" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="20"/>
       <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P18" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q18" s="20"/>
       <c r="R18"/>
@@ -2956,38 +3159,38 @@
         <v>42</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="H19" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K19" s="30"/>
+        <v>416</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>368</v>
+      </c>
+      <c r="H19" s="21">
+        <v>128.5</v>
+      </c>
+      <c r="I19" s="36"/>
+      <c r="J19" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K19" s="29"/>
       <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20" t="s">
-        <v>319</v>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29" t="s">
+        <v>356</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q19" s="20"/>
       <c r="R19"/>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" s="37" customFormat="1">
       <c r="A20" s="22" t="s">
         <v>40</v>
       </c>
@@ -2997,37 +3200,38 @@
       <c r="C20" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>244</v>
+      <c r="D20" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>368</v>
       </c>
       <c r="H20" s="21">
-        <v>118.3</v>
-      </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K20" s="30"/>
+        <v>133.1</v>
+      </c>
+      <c r="I20" s="36"/>
+      <c r="J20" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K20" s="29"/>
       <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29" t="s">
+        <v>369</v>
+      </c>
       <c r="P20" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q20" s="20"/>
-      <c r="R20"/>
-    </row>
-    <row r="21" spans="1:18">
+    </row>
+    <row r="21" spans="1:18" s="37" customFormat="1">
       <c r="A21" s="22" t="s">
         <v>40</v>
       </c>
@@ -3037,37 +3241,38 @@
       <c r="C21" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>244</v>
+      <c r="D21" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>368</v>
       </c>
       <c r="H21" s="21">
-        <v>132.5</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K21" s="30"/>
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I21" s="36"/>
+      <c r="J21" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K21" s="29"/>
       <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29" t="s">
+        <v>356</v>
+      </c>
       <c r="P21" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q21" s="20"/>
-      <c r="R21"/>
-    </row>
-    <row r="22" spans="1:18">
+    </row>
+    <row r="22" spans="1:18" s="37" customFormat="1">
       <c r="A22" s="22" t="s">
         <v>40</v>
       </c>
@@ -3077,37 +3282,38 @@
       <c r="C22" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>244</v>
+      <c r="D22" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>368</v>
       </c>
       <c r="H22" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K22" s="30"/>
+        <v>124.75</v>
+      </c>
+      <c r="I22" s="36"/>
+      <c r="J22" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K22" s="29"/>
       <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29" t="s">
+        <v>398</v>
+      </c>
       <c r="P22" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q22" s="20"/>
-      <c r="R22"/>
-    </row>
-    <row r="23" spans="1:18">
+    </row>
+    <row r="23" spans="1:18" s="37" customFormat="1">
       <c r="A23" s="22" t="s">
         <v>40</v>
       </c>
@@ -3117,35 +3323,34 @@
       <c r="C23" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>297</v>
+      <c r="D23" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>222</v>
       </c>
       <c r="H23" s="21">
         <v>126.9</v>
       </c>
-      <c r="I23" s="30"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="20"/>
+        <v>289</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="20"/>
       <c r="O23" s="20"/>
       <c r="P23" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q23" s="20"/>
-      <c r="R23"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="22" t="s">
@@ -3157,32 +3362,32 @@
       <c r="C24" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="H24" s="28">
-        <v>121.5</v>
-      </c>
-      <c r="I24" s="30"/>
-      <c r="J24" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K24" s="30"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
+      <c r="D24" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="21">
+        <v>118.1</v>
+      </c>
+      <c r="I24" s="29"/>
+      <c r="J24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
       <c r="O24" s="20"/>
       <c r="P24" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q24" s="20"/>
       <c r="R24"/>
@@ -3198,36 +3403,38 @@
         <v>42</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="H25" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I25" s="30"/>
-      <c r="J25" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K25" s="30"/>
+        <v>221</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I25" s="29"/>
+      <c r="J25" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K25" s="29"/>
       <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P25" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q25" s="20"/>
       <c r="R25"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" s="37" customFormat="1">
       <c r="A26" s="22" t="s">
         <v>40</v>
       </c>
@@ -3237,39 +3444,38 @@
       <c r="C26" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="H26" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I26" s="30"/>
-      <c r="J26" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K26" s="30"/>
+      <c r="D26" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="H26" s="21">
+        <v>128.1</v>
+      </c>
+      <c r="I26" s="36"/>
+      <c r="J26" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="K26" s="29"/>
       <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20" t="s">
-        <v>319</v>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29" t="s">
+        <v>356</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q26" s="20"/>
-      <c r="R26"/>
-    </row>
-    <row r="27" spans="1:18">
+    </row>
+    <row r="27" spans="1:18" s="37" customFormat="1">
       <c r="A27" s="22" t="s">
         <v>40</v>
       </c>
@@ -3279,37 +3485,38 @@
       <c r="C27" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H27" s="25">
-        <v>120.6</v>
-      </c>
-      <c r="I27" s="30"/>
-      <c r="J27" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="K27" s="30"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="20"/>
+      <c r="D27" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="H27" s="21">
+        <v>124.3</v>
+      </c>
+      <c r="I27" s="36"/>
+      <c r="J27" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="K27" s="29"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29" t="s">
+        <v>361</v>
+      </c>
       <c r="P27" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q27" s="20"/>
-      <c r="R27"/>
-    </row>
-    <row r="28" spans="1:18">
+    </row>
+    <row r="28" spans="1:18" s="37" customFormat="1">
       <c r="A28" s="22" t="s">
         <v>40</v>
       </c>
@@ -3319,117 +3526,118 @@
       <c r="C28" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H28" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I28" s="30"/>
-      <c r="J28" s="20" t="s">
+      <c r="D28" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="H28" s="21">
+        <v>128.5</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K28" s="29"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="P28" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="37" customFormat="1">
+      <c r="A29" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="H29" s="21">
+        <v>133.1</v>
+      </c>
+      <c r="I29" s="36"/>
+      <c r="J29" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K29" s="29"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="P29" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="37" customFormat="1">
+      <c r="A30" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="H30" s="24">
+        <v>120.1</v>
+      </c>
+      <c r="I30" s="29"/>
+      <c r="J30" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q28" s="20"/>
-      <c r="R28"/>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H29" s="25">
-        <v>121.9</v>
-      </c>
-      <c r="I29" s="30"/>
-      <c r="J29" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="K29" s="30"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q29" s="20"/>
-      <c r="R29"/>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H30" s="25">
-        <v>127</v>
-      </c>
-      <c r="I30" s="30"/>
-      <c r="J30" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="K30" s="30"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="20"/>
       <c r="O30" s="20"/>
       <c r="P30" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q30" s="20"/>
-      <c r="R30"/>
-    </row>
-    <row r="31" spans="1:18">
+    </row>
+    <row r="31" spans="1:18" s="37" customFormat="1">
       <c r="A31" s="22" t="s">
         <v>40</v>
       </c>
@@ -3440,34 +3648,33 @@
         <v>42</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H31" s="25">
+        <v>272</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="H31" s="24">
         <v>121.5</v>
       </c>
-      <c r="I31" s="30"/>
+      <c r="I31" s="29"/>
       <c r="J31" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K31" s="30"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K31" s="29"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
       <c r="O31" s="20"/>
       <c r="P31" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q31" s="20"/>
-      <c r="R31"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="22" t="s">
@@ -3480,33 +3687,31 @@
         <v>42</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>327</v>
+        <v>106</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H32" s="21">
+        <v>295</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H32" s="24">
         <v>126.9</v>
       </c>
-      <c r="I32" s="30"/>
+      <c r="I32" s="29"/>
       <c r="J32" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
+        <v>298</v>
+      </c>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
       <c r="N32" s="20"/>
-      <c r="O32" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="O32" s="20"/>
       <c r="P32" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q32" s="20"/>
       <c r="R32"/>
@@ -3522,31 +3727,33 @@
         <v>42</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G33" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="H33" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I33" s="30"/>
+        <v>295</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H33" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I33" s="29"/>
       <c r="J33" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
       <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
+      <c r="O33" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P33" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q33" s="20"/>
       <c r="R33"/>
@@ -3561,32 +3768,32 @@
       <c r="C34" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G34" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="H34" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I34" s="30"/>
+      <c r="D34" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="H34" s="21">
+        <v>118.3</v>
+      </c>
+      <c r="I34" s="29"/>
       <c r="J34" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
+        <v>310</v>
+      </c>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
       <c r="N34" s="20"/>
       <c r="O34" s="20"/>
       <c r="P34" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q34" s="20"/>
       <c r="R34"/>
@@ -3601,32 +3808,32 @@
       <c r="C35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="F35" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G35" s="24" t="s">
-        <v>266</v>
+      <c r="D35" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>239</v>
       </c>
       <c r="H35" s="21">
-        <v>124.1</v>
-      </c>
-      <c r="I35" s="30"/>
+        <v>132.5</v>
+      </c>
+      <c r="I35" s="29"/>
       <c r="J35" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
       <c r="N35" s="20"/>
       <c r="O35" s="20"/>
       <c r="P35" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q35" s="20"/>
       <c r="R35"/>
@@ -3641,32 +3848,32 @@
       <c r="C36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="H36" s="25">
-        <v>118.5</v>
-      </c>
-      <c r="I36" s="30"/>
-      <c r="J36" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="30"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
+      <c r="D36" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="H36" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I36" s="29"/>
+      <c r="J36" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="20"/>
       <c r="O36" s="20"/>
       <c r="P36" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q36" s="20"/>
       <c r="R36"/>
@@ -3682,31 +3889,31 @@
         <v>42</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="H37" s="21">
-        <v>132.5</v>
-      </c>
-      <c r="I37" s="30"/>
+        <v>218</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="H37" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I37" s="29"/>
       <c r="J37" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
+        <v>298</v>
+      </c>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
       <c r="N37" s="20"/>
       <c r="O37" s="20"/>
       <c r="P37" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q37" s="20"/>
       <c r="R37"/>
@@ -3722,31 +3929,33 @@
         <v>42</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="H38" s="21">
+        <v>218</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="H38" s="24">
         <v>121.5</v>
       </c>
-      <c r="I38" s="30"/>
+      <c r="I38" s="29"/>
       <c r="J38" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
       <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
+      <c r="O38" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P38" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q38" s="20"/>
       <c r="R38"/>
@@ -3761,32 +3970,32 @@
       <c r="C39" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="H39" s="21">
-        <v>126.9</v>
-      </c>
-      <c r="I39" s="30"/>
-      <c r="J39" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K39" s="30"/>
+      <c r="D39" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" s="24">
+        <v>120.6</v>
+      </c>
+      <c r="I39" s="29"/>
+      <c r="J39" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="K39" s="29"/>
       <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="20"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
       <c r="O39" s="20"/>
       <c r="P39" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q39" s="20"/>
       <c r="R39"/>
@@ -3801,32 +4010,32 @@
       <c r="C40" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="H40" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I40" s="30"/>
+      <c r="D40" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H40" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I40" s="29"/>
       <c r="J40" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
+        <v>46</v>
+      </c>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
       <c r="N40" s="20"/>
       <c r="O40" s="20"/>
       <c r="P40" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q40" s="20"/>
       <c r="R40"/>
@@ -3841,32 +4050,32 @@
       <c r="C41" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="H41" s="21">
-        <v>126.9</v>
-      </c>
-      <c r="I41" s="30"/>
-      <c r="J41" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K41" s="30"/>
+      <c r="D41" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F41" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H41" s="24">
+        <v>121.9</v>
+      </c>
+      <c r="I41" s="29"/>
+      <c r="J41" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="K41" s="29"/>
       <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="20"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
       <c r="O41" s="20"/>
       <c r="P41" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q41" s="20"/>
       <c r="R41"/>
@@ -3881,34 +4090,32 @@
       <c r="C42" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="H42" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I42" s="30"/>
-      <c r="J42" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K42" s="30"/>
+      <c r="D42" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H42" s="24">
+        <v>127</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="K42" s="29"/>
       <c r="L42" s="30"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="20"/>
       <c r="P42" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q42" s="20"/>
       <c r="R42"/>
@@ -3924,31 +4131,31 @@
         <v>42</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>71</v>
+        <v>314</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="G43" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="H43" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I43" s="30"/>
-      <c r="J43" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="K43" s="30"/>
+        <v>235</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H43" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I43" s="29"/>
+      <c r="J43" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K43" s="29"/>
       <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="30"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="20"/>
       <c r="P43" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q43" s="20"/>
       <c r="R43"/>
@@ -3964,33 +4171,33 @@
         <v>42</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>71</v>
+        <v>314</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="G44" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="H44" s="25">
+        <v>235</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H44" s="21">
         <v>126.9</v>
       </c>
-      <c r="I44" s="30"/>
-      <c r="J44" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="K44" s="30"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="20"/>
       <c r="O44" s="20" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q44" s="20"/>
       <c r="R44"/>
@@ -4005,34 +4212,32 @@
       <c r="C45" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="G45" s="24" t="s">
-        <v>229</v>
+      <c r="D45" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>286</v>
       </c>
       <c r="H45" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I45" s="30"/>
+        <v>126.9</v>
+      </c>
+      <c r="I45" s="29"/>
       <c r="J45" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
+        <v>312</v>
+      </c>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="20"/>
       <c r="N45" s="20"/>
-      <c r="O45" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="O45" s="20"/>
       <c r="P45" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q45" s="20"/>
       <c r="R45"/>
@@ -4047,32 +4252,32 @@
       <c r="C46" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="H46" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I46" s="30"/>
-      <c r="J46" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K46" s="30"/>
+      <c r="D46" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="H46" s="27">
+        <v>121.5</v>
+      </c>
+      <c r="I46" s="29"/>
+      <c r="J46" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K46" s="29"/>
       <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="20"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
       <c r="O46" s="20"/>
       <c r="P46" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q46" s="20"/>
       <c r="R46"/>
@@ -4088,31 +4293,31 @@
         <v>42</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>333</v>
+        <v>127</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="H47" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I47" s="30"/>
+        <v>279</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I47" s="29"/>
       <c r="J47" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
+        <v>312</v>
+      </c>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
       <c r="N47" s="20"/>
       <c r="O47" s="20"/>
       <c r="P47" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q47" s="20"/>
       <c r="R47"/>
@@ -4128,31 +4333,31 @@
         <v>42</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>334</v>
+        <v>127</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="G48" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="H48" s="25">
-        <v>118.3</v>
-      </c>
-      <c r="I48" s="30"/>
+        <v>279</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="H48" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I48" s="29"/>
       <c r="J48" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
       <c r="N48" s="20"/>
       <c r="O48" s="20"/>
       <c r="P48" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q48" s="20"/>
       <c r="R48"/>
@@ -4168,33 +4373,31 @@
         <v>42</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="H49" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I49" s="30"/>
+        <v>256</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="H49" s="21">
+        <v>124.1</v>
+      </c>
+      <c r="I49" s="29"/>
       <c r="J49" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
+        <v>315</v>
+      </c>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
       <c r="N49" s="20"/>
-      <c r="O49" s="30" t="s">
-        <v>319</v>
-      </c>
+      <c r="O49" s="20"/>
       <c r="P49" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q49" s="20"/>
       <c r="R49"/>
@@ -4210,31 +4413,31 @@
         <v>42</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="G50" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H50" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I50" s="30"/>
+        <v>256</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="H50" s="24">
+        <v>118.5</v>
+      </c>
+      <c r="I50" s="29"/>
       <c r="J50" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="K50" s="30"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30"/>
+        <v>46</v>
+      </c>
+      <c r="K50" s="29"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
       <c r="O50" s="20"/>
       <c r="P50" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q50" s="20"/>
       <c r="R50"/>
@@ -4250,31 +4453,31 @@
         <v>42</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="G51" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H51" s="25">
-        <v>121.9</v>
-      </c>
-      <c r="I51" s="30"/>
+        <v>256</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="21">
+        <v>132.5</v>
+      </c>
+      <c r="I51" s="29"/>
       <c r="J51" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
       <c r="N51" s="20"/>
       <c r="O51" s="20"/>
       <c r="P51" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q51" s="20"/>
       <c r="R51"/>
@@ -4290,36 +4493,36 @@
         <v>42</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="F52" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="G52" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H52" s="25">
-        <v>132.5</v>
-      </c>
-      <c r="I52" s="30"/>
+        <v>256</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="G52" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="H52" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I52" s="29"/>
       <c r="J52" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
       <c r="N52" s="20"/>
       <c r="O52" s="20"/>
       <c r="P52" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q52" s="20"/>
       <c r="R52"/>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:18" s="37" customFormat="1">
       <c r="A53" s="22" t="s">
         <v>40</v>
       </c>
@@ -4330,36 +4533,37 @@
         <v>42</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="F53" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="G53" s="24" t="s">
-        <v>238</v>
+        <v>256</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>390</v>
       </c>
       <c r="H53" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I53" s="30"/>
-      <c r="J53" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K53" s="30"/>
+        <v>128.5</v>
+      </c>
+      <c r="I53" s="36"/>
+      <c r="J53" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K53" s="29"/>
       <c r="L53" s="30"/>
-      <c r="M53" s="30"/>
+      <c r="M53" s="29"/>
       <c r="N53" s="20"/>
-      <c r="O53" s="20"/>
+      <c r="O53" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P53" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q53" s="20"/>
-      <c r="R53"/>
-    </row>
-    <row r="54" spans="1:18">
+    </row>
+    <row r="54" spans="1:18" s="37" customFormat="1">
       <c r="A54" s="22" t="s">
         <v>40</v>
       </c>
@@ -4370,34 +4574,35 @@
         <v>42</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H54" s="25">
-        <v>118.3</v>
-      </c>
-      <c r="I54" s="30"/>
-      <c r="J54" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K54" s="30"/>
+        <v>256</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="H54" s="21">
+        <v>133.1</v>
+      </c>
+      <c r="I54" s="36"/>
+      <c r="J54" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K54" s="29"/>
       <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
+      <c r="M54" s="29"/>
       <c r="N54" s="20"/>
-      <c r="O54" s="30"/>
+      <c r="O54" s="20" t="s">
+        <v>369</v>
+      </c>
       <c r="P54" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q54" s="20"/>
-      <c r="R54"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="22" t="s">
@@ -4409,32 +4614,32 @@
       <c r="C55" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F55" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H55" s="25">
-        <v>121.9</v>
-      </c>
-      <c r="I55" s="30"/>
-      <c r="J55" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="K55" s="30"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
+      <c r="D55" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="H55" s="21">
+        <v>126.9</v>
+      </c>
+      <c r="I55" s="29"/>
+      <c r="J55" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="20"/>
       <c r="O55" s="20"/>
       <c r="P55" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q55" s="20"/>
       <c r="R55"/>
@@ -4449,32 +4654,32 @@
       <c r="C56" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D56" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H56" s="25">
-        <v>132.94999999999999</v>
-      </c>
-      <c r="I56" s="30"/>
+      <c r="D56" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="H56" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I56" s="29"/>
       <c r="J56" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K56" s="30"/>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
       <c r="N56" s="20"/>
       <c r="O56" s="20"/>
       <c r="P56" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q56" s="20"/>
       <c r="R56"/>
@@ -4489,32 +4694,32 @@
       <c r="C57" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D57" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H57" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I57" s="30"/>
-      <c r="J57" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K57" s="30"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="30"/>
+      <c r="D57" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="H57" s="21">
+        <v>126.9</v>
+      </c>
+      <c r="I57" s="29"/>
+      <c r="J57" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="20"/>
       <c r="O57" s="20"/>
       <c r="P57" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q57" s="20"/>
       <c r="R57"/>
@@ -4529,34 +4734,34 @@
       <c r="C58" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D58" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F58" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G58" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H58" s="25">
-        <v>119.75</v>
-      </c>
-      <c r="I58" s="30"/>
-      <c r="J58" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="K58" s="30"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
+      <c r="D58" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G58" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="H58" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I58" s="29"/>
+      <c r="J58" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
       <c r="O58" s="20" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q58" s="20"/>
       <c r="R58"/>
@@ -4572,33 +4777,31 @@
         <v>42</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>337</v>
+        <v>71</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F59" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="G59" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H59" s="21">
-        <v>126.9</v>
-      </c>
-      <c r="I59" s="30"/>
+        <v>225</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="G59" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="H59" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I59" s="29"/>
       <c r="J59" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="30"/>
+        <v>125</v>
+      </c>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
       <c r="N59" s="20"/>
-      <c r="O59" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="O59" s="29"/>
       <c r="P59" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q59" s="20"/>
       <c r="R59"/>
@@ -4613,32 +4816,34 @@
       <c r="C60" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D60" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="F60" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="G60" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="H60" s="21">
-        <v>118.4</v>
-      </c>
-      <c r="I60" s="30"/>
-      <c r="J60" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K60" s="30"/>
+      <c r="D60" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="H60" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I60" s="29"/>
+      <c r="J60" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K60" s="29"/>
       <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P60" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q60" s="20"/>
       <c r="R60"/>
@@ -4653,32 +4858,34 @@
       <c r="C61" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D61" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="G61" s="24" t="s">
-        <v>262</v>
+      <c r="D61" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>227</v>
       </c>
       <c r="H61" s="21">
-        <v>132.9</v>
-      </c>
-      <c r="I61" s="30"/>
+        <v>121.5</v>
+      </c>
+      <c r="I61" s="29"/>
       <c r="J61" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
       <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
+      <c r="O61" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P61" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q61" s="20"/>
       <c r="R61"/>
@@ -4693,32 +4900,32 @@
       <c r="C62" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D62" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="G62" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="H62" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I62" s="30"/>
+      <c r="D62" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="H62" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I62" s="29"/>
       <c r="J62" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K62" s="30"/>
-      <c r="L62" s="30"/>
-      <c r="M62" s="30"/>
+        <v>310</v>
+      </c>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
       <c r="N62" s="20"/>
       <c r="O62" s="20"/>
       <c r="P62" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q62" s="20"/>
       <c r="R62"/>
@@ -4733,37 +4940,37 @@
       <c r="C63" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D63" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F63" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G63" s="24" t="s">
-        <v>217</v>
+      <c r="D63" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>229</v>
       </c>
       <c r="H63" s="21">
-        <v>118.1</v>
-      </c>
-      <c r="I63" s="30"/>
+        <v>121.5</v>
+      </c>
+      <c r="I63" s="29"/>
       <c r="J63" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K63" s="30"/>
-      <c r="L63" s="30"/>
-      <c r="M63" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
       <c r="N63" s="20"/>
       <c r="O63" s="20"/>
       <c r="P63" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q63" s="20"/>
       <c r="R63"/>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" s="37" customFormat="1">
       <c r="A64" s="22" t="s">
         <v>40</v>
       </c>
@@ -4773,37 +4980,38 @@
       <c r="C64" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D64" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F64" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G64" s="24" t="s">
-        <v>217</v>
+      <c r="D64" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="G64" s="33" t="s">
+        <v>229</v>
       </c>
       <c r="H64" s="21">
-        <v>130.9</v>
-      </c>
-      <c r="I64" s="30"/>
-      <c r="J64" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K64" s="30"/>
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I64" s="36"/>
+      <c r="J64" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K64" s="29"/>
       <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
+      <c r="M64" s="29"/>
       <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
+      <c r="O64" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P64" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q64" s="20"/>
-      <c r="R64"/>
-    </row>
-    <row r="65" spans="1:18">
+    </row>
+    <row r="65" spans="1:18" s="37" customFormat="1">
       <c r="A65" s="22" t="s">
         <v>40</v>
       </c>
@@ -4813,35 +5021,36 @@
       <c r="C65" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G65" s="24" t="s">
-        <v>217</v>
+      <c r="D65" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="G65" s="33" t="s">
+        <v>229</v>
       </c>
       <c r="H65" s="21">
-        <v>121.5</v>
-      </c>
-      <c r="I65" s="30"/>
-      <c r="J65" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K65" s="30"/>
+        <v>124.75</v>
+      </c>
+      <c r="I65" s="36"/>
+      <c r="J65" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K65" s="29"/>
       <c r="L65" s="30"/>
-      <c r="M65" s="30"/>
+      <c r="M65" s="29"/>
       <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
+      <c r="O65" s="20" t="s">
+        <v>398</v>
+      </c>
       <c r="P65" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q65" s="20"/>
-      <c r="R65"/>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="22" t="s">
@@ -4853,34 +5062,32 @@
       <c r="C66" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F66" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G66" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="H66" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I66" s="30"/>
+      <c r="D66" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G66" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" s="24">
+        <v>119.7</v>
+      </c>
+      <c r="I66" s="29"/>
       <c r="J66" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K66" s="30"/>
-      <c r="L66" s="30"/>
-      <c r="M66" s="30"/>
+        <v>315</v>
+      </c>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="29"/>
       <c r="N66" s="20"/>
-      <c r="O66" s="30" t="s">
-        <v>319</v>
-      </c>
+      <c r="O66" s="20"/>
       <c r="P66" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q66" s="20"/>
       <c r="R66"/>
@@ -4896,31 +5103,31 @@
         <v>42</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="G67" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="H67" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I67" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G67" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="24">
+        <v>126.6</v>
+      </c>
+      <c r="I67" s="29"/>
       <c r="J67" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
+        <v>337</v>
+      </c>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
       <c r="N67" s="20"/>
       <c r="O67" s="20"/>
       <c r="P67" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q67" s="20"/>
       <c r="R67"/>
@@ -4936,31 +5143,31 @@
         <v>42</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="G68" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="H68" s="25">
-        <v>118.5</v>
-      </c>
-      <c r="I68" s="30"/>
-      <c r="J68" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K68" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" s="24">
+        <v>119.5</v>
+      </c>
+      <c r="I68" s="29"/>
+      <c r="J68" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="K68" s="29"/>
       <c r="L68" s="30"/>
-      <c r="M68" s="30"/>
-      <c r="N68" s="20"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
       <c r="O68" s="20"/>
       <c r="P68" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q68" s="20"/>
       <c r="R68"/>
@@ -4976,31 +5183,31 @@
         <v>42</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="G69" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="H69" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I69" s="30"/>
-      <c r="J69" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K69" s="30"/>
-      <c r="L69" s="30"/>
-      <c r="M69" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G69" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" s="21">
+        <v>133.9</v>
+      </c>
+      <c r="I69" s="29"/>
+      <c r="J69" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="20"/>
       <c r="N69" s="20"/>
       <c r="O69" s="20"/>
       <c r="P69" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q69" s="20"/>
       <c r="R69"/>
@@ -5016,33 +5223,31 @@
         <v>42</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>187</v>
+        <v>349</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="F70" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="G70" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H70" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I70" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G70" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H70" s="21">
+        <v>135</v>
+      </c>
+      <c r="I70" s="29"/>
       <c r="J70" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
+        <v>338</v>
+      </c>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
       <c r="N70" s="20"/>
-      <c r="O70" s="20" t="s">
-        <v>341</v>
-      </c>
+      <c r="O70" s="20"/>
       <c r="P70" s="20" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="Q70" s="20"/>
       <c r="R70"/>
@@ -5058,33 +5263,31 @@
         <v>42</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>187</v>
+        <v>349</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="F71" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="G71" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H71" s="25">
-        <v>118.3</v>
-      </c>
-      <c r="I71" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G71" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="21">
+        <v>119.1</v>
+      </c>
+      <c r="I71" s="29"/>
       <c r="J71" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K71" s="30"/>
-      <c r="L71" s="30"/>
-      <c r="M71" s="30"/>
+        <v>339</v>
+      </c>
+      <c r="K71" s="29"/>
+      <c r="L71" s="29"/>
+      <c r="M71" s="20"/>
       <c r="N71" s="20"/>
-      <c r="O71" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="O71" s="20"/>
       <c r="P71" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q71" s="20"/>
       <c r="R71"/>
@@ -5100,33 +5303,31 @@
         <v>42</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>187</v>
+        <v>349</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="F72" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="G72" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H72" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I72" s="30"/>
-      <c r="J72" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K72" s="30"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="30"/>
-      <c r="N72" s="30"/>
-      <c r="O72" s="20" t="s">
-        <v>319</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G72" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H72" s="21">
+        <v>128.1</v>
+      </c>
+      <c r="I72" s="29"/>
+      <c r="J72" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="K72" s="29"/>
+      <c r="L72" s="29"/>
+      <c r="M72" s="29"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="20"/>
       <c r="P72" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q72" s="20"/>
       <c r="R72"/>
@@ -5142,31 +5343,31 @@
         <v>42</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F73" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="G73" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="H73" s="25">
-        <v>118.4</v>
-      </c>
-      <c r="I73" s="30"/>
-      <c r="J73" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="K73" s="30"/>
-      <c r="L73" s="31"/>
-      <c r="M73" s="30"/>
-      <c r="N73" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G73" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H73" s="21">
+        <v>124.3</v>
+      </c>
+      <c r="I73" s="29"/>
+      <c r="J73" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="K73" s="29"/>
+      <c r="L73" s="29"/>
+      <c r="M73" s="29"/>
+      <c r="N73" s="20"/>
       <c r="O73" s="20"/>
       <c r="P73" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q73" s="20"/>
       <c r="R73"/>
@@ -5182,31 +5383,31 @@
         <v>42</v>
       </c>
       <c r="D74" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G74" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" s="24">
+        <v>128.5</v>
+      </c>
+      <c r="I74" s="29"/>
+      <c r="J74" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="E74" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F74" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="G74" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="H74" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I74" s="30"/>
-      <c r="J74" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K74" s="30"/>
-      <c r="L74" s="30"/>
-      <c r="M74" s="30"/>
+      <c r="K74" s="29"/>
+      <c r="L74" s="29"/>
+      <c r="M74" s="29"/>
       <c r="N74" s="20"/>
-      <c r="O74" s="20"/>
+      <c r="O74" s="29"/>
       <c r="P74" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q74" s="20"/>
       <c r="R74"/>
@@ -5222,33 +5423,31 @@
         <v>42</v>
       </c>
       <c r="D75" s="22" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F75" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="G75" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="H75" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I75" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G75" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" s="24">
+        <v>133.1</v>
+      </c>
+      <c r="I75" s="29"/>
       <c r="J75" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="K75" s="30"/>
-      <c r="L75" s="30"/>
-      <c r="M75" s="30"/>
+        <v>343</v>
+      </c>
+      <c r="K75" s="29"/>
+      <c r="L75" s="29"/>
+      <c r="M75" s="29"/>
       <c r="N75" s="20"/>
-      <c r="O75" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="O75" s="20"/>
       <c r="P75" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q75" s="20"/>
       <c r="R75"/>
@@ -5264,31 +5463,31 @@
         <v>42</v>
       </c>
       <c r="D76" s="22" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="F76" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="G76" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="H76" s="25">
-        <v>119.5</v>
-      </c>
-      <c r="I76" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G76" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H76" s="24">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I76" s="29"/>
       <c r="J76" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="K76" s="30"/>
-      <c r="L76" s="31"/>
-      <c r="M76" s="30"/>
-      <c r="N76" s="30"/>
+        <v>344</v>
+      </c>
+      <c r="K76" s="29"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29"/>
       <c r="O76" s="20"/>
       <c r="P76" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q76" s="20"/>
       <c r="R76"/>
@@ -5304,31 +5503,31 @@
         <v>42</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="F77" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="G77" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="H77" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I77" s="30"/>
-      <c r="J77" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K77" s="30"/>
-      <c r="L77" s="30"/>
-      <c r="M77" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G77" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H77" s="24">
+        <v>124.75</v>
+      </c>
+      <c r="I77" s="29"/>
+      <c r="J77" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="K77" s="29"/>
+      <c r="L77" s="29"/>
+      <c r="M77" s="29"/>
       <c r="N77" s="20"/>
-      <c r="O77" s="20"/>
+      <c r="O77" s="29"/>
       <c r="P77" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q77" s="20"/>
       <c r="R77"/>
@@ -5344,31 +5543,31 @@
         <v>42</v>
       </c>
       <c r="D78" s="22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H78" s="25">
-        <v>118.4</v>
-      </c>
-      <c r="I78" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H78" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I78" s="29"/>
       <c r="J78" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K78" s="30"/>
-      <c r="L78" s="30"/>
-      <c r="M78" s="20"/>
+        <v>46</v>
+      </c>
+      <c r="K78" s="29"/>
+      <c r="L78" s="29"/>
+      <c r="M78" s="29"/>
       <c r="N78" s="20"/>
       <c r="O78" s="20"/>
       <c r="P78" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q78" s="20"/>
       <c r="R78"/>
@@ -5384,36 +5583,36 @@
         <v>42</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F79" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="G79" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H79" s="25">
-        <v>130.85</v>
-      </c>
-      <c r="I79" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F79" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G79" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H79" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I79" s="29"/>
       <c r="J79" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K79" s="30"/>
-      <c r="L79" s="30"/>
-      <c r="M79" s="20"/>
+        <v>346</v>
+      </c>
+      <c r="K79" s="29"/>
+      <c r="L79" s="29"/>
+      <c r="M79" s="29"/>
       <c r="N79" s="20"/>
       <c r="O79" s="20"/>
       <c r="P79" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q79" s="20"/>
       <c r="R79"/>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" s="37" customFormat="1">
       <c r="A80" s="22" t="s">
         <v>40</v>
       </c>
@@ -5424,36 +5623,35 @@
         <v>42</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F80" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H80" s="24">
+        <v>121.9</v>
+      </c>
+      <c r="I80" s="29"/>
+      <c r="J80" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="G80" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H80" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I80" s="30"/>
-      <c r="J80" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K80" s="30"/>
+      <c r="K80" s="29"/>
       <c r="L80" s="30"/>
-      <c r="M80" s="20"/>
-      <c r="N80" s="20"/>
+      <c r="M80" s="29"/>
+      <c r="N80" s="29"/>
       <c r="O80" s="20"/>
       <c r="P80" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q80" s="20"/>
-      <c r="R80"/>
-    </row>
-    <row r="81" spans="1:18">
+    </row>
+    <row r="81" spans="1:18" s="37" customFormat="1">
       <c r="A81" s="22" t="s">
         <v>40</v>
       </c>
@@ -5464,36 +5662,33 @@
         <v>42</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F81" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="G81" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H81" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I81" s="30"/>
-      <c r="J81" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="K81" s="30"/>
-      <c r="L81" s="31"/>
-      <c r="M81" s="30"/>
-      <c r="N81" s="30"/>
-      <c r="O81" s="20" t="s">
-        <v>319</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G81" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H81" s="24">
+        <v>127.3</v>
+      </c>
+      <c r="I81" s="29"/>
+      <c r="J81" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="K81" s="29"/>
+      <c r="L81" s="29"/>
+      <c r="M81" s="29"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
       <c r="P81" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q81" s="20"/>
-      <c r="R81"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="22" t="s">
@@ -5506,31 +5701,31 @@
         <v>42</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F82" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="G82" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="H82" s="25">
-        <v>118.7</v>
-      </c>
-      <c r="I82" s="30"/>
-      <c r="J82" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="K82" s="30"/>
-      <c r="L82" s="31"/>
-      <c r="M82" s="30"/>
-      <c r="N82" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G82" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H82" s="21">
+        <v>118.5</v>
+      </c>
+      <c r="I82" s="29"/>
+      <c r="J82" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="K82" s="29"/>
+      <c r="L82" s="29"/>
+      <c r="M82" s="20"/>
+      <c r="N82" s="20"/>
       <c r="O82" s="20"/>
       <c r="P82" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q82" s="20"/>
       <c r="R82"/>
@@ -5546,31 +5741,31 @@
         <v>42</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F83" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="G83" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="H83" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I83" s="30"/>
-      <c r="J83" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="K83" s="30"/>
-      <c r="L83" s="31"/>
-      <c r="M83" s="30"/>
-      <c r="N83" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F83" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G83" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H83" s="21">
+        <v>127.9</v>
+      </c>
+      <c r="I83" s="29"/>
+      <c r="J83" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K83" s="29"/>
+      <c r="L83" s="29"/>
+      <c r="M83" s="29"/>
+      <c r="N83" s="20"/>
       <c r="O83" s="20"/>
       <c r="P83" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q83" s="20"/>
       <c r="R83"/>
@@ -5586,38 +5781,36 @@
         <v>42</v>
       </c>
       <c r="D84" s="22" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F84" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="G84" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="H84" s="25">
+        <v>223</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G84" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H84" s="24">
         <v>121.5</v>
       </c>
-      <c r="I84" s="30"/>
-      <c r="J84" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K84" s="30"/>
-      <c r="L84" s="31"/>
-      <c r="M84" s="30"/>
-      <c r="N84" s="30"/>
-      <c r="O84" s="20" t="s">
-        <v>319</v>
-      </c>
+      <c r="I84" s="29"/>
+      <c r="J84" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K84" s="29"/>
+      <c r="L84" s="29"/>
+      <c r="M84" s="29"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="20"/>
       <c r="P84" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q84" s="20"/>
       <c r="R84"/>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" s="37" customFormat="1">
       <c r="A85" s="22" t="s">
         <v>40</v>
       </c>
@@ -5628,36 +5821,35 @@
         <v>42</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F85" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="G85" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="H85" s="25">
-        <v>118.7</v>
-      </c>
-      <c r="I85" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G85" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H85" s="27">
+        <v>121.75</v>
+      </c>
+      <c r="I85" s="29"/>
       <c r="J85" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="K85" s="30"/>
-      <c r="L85" s="31"/>
-      <c r="M85" s="30"/>
-      <c r="N85" s="30"/>
+        <v>350</v>
+      </c>
+      <c r="K85" s="29"/>
+      <c r="L85" s="30"/>
+      <c r="M85" s="29"/>
+      <c r="N85" s="29"/>
       <c r="O85" s="20"/>
       <c r="P85" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q85" s="20"/>
-      <c r="R85"/>
-    </row>
-    <row r="86" spans="1:18">
+    </row>
+    <row r="86" spans="1:18" s="37" customFormat="1">
       <c r="A86" s="22" t="s">
         <v>40</v>
       </c>
@@ -5668,34 +5860,33 @@
         <v>42</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="G86" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="H86" s="25">
-        <v>132.75</v>
-      </c>
-      <c r="I86" s="30"/>
-      <c r="J86" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K86" s="30"/>
-      <c r="L86" s="30"/>
-      <c r="M86" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F86" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G86" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H86" s="21">
+        <v>126.1</v>
+      </c>
+      <c r="I86" s="29"/>
+      <c r="J86" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="K86" s="29"/>
+      <c r="L86" s="29"/>
+      <c r="M86" s="20"/>
       <c r="N86" s="20"/>
       <c r="O86" s="20"/>
       <c r="P86" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q86" s="20"/>
-      <c r="R86"/>
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="22" t="s">
@@ -5708,31 +5899,31 @@
         <v>42</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F87" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="G87" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="H87" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I87" s="30"/>
-      <c r="J87" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K87" s="30"/>
-      <c r="L87" s="31"/>
-      <c r="M87" s="30"/>
-      <c r="N87" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F87" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G87" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H87" s="27">
+        <v>118.75</v>
+      </c>
+      <c r="I87" s="29"/>
+      <c r="J87" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="K87" s="29"/>
+      <c r="L87" s="29"/>
+      <c r="M87" s="29"/>
+      <c r="N87" s="20"/>
       <c r="O87" s="20"/>
       <c r="P87" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q87" s="20"/>
       <c r="R87"/>
@@ -5748,31 +5939,31 @@
         <v>42</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="F88" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="G88" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="H88" s="25">
-        <v>126.8</v>
-      </c>
-      <c r="I88" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F88" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H88" s="27">
+        <v>118.9</v>
+      </c>
+      <c r="I88" s="29"/>
       <c r="J88" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="K88" s="30"/>
+        <v>353</v>
+      </c>
+      <c r="K88" s="29"/>
       <c r="L88" s="30"/>
-      <c r="M88" s="30"/>
+      <c r="M88" s="29"/>
       <c r="N88" s="20"/>
-      <c r="O88" s="30"/>
+      <c r="O88" s="29"/>
       <c r="P88" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q88" s="20"/>
       <c r="R88"/>
@@ -5788,31 +5979,31 @@
         <v>42</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="F89" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="G89" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="H89" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I89" s="30"/>
-      <c r="J89" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K89" s="30"/>
+        <v>223</v>
+      </c>
+      <c r="F89" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G89" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H89" s="27">
+        <v>126.9</v>
+      </c>
+      <c r="I89" s="29"/>
+      <c r="J89" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="K89" s="29"/>
       <c r="L89" s="30"/>
-      <c r="M89" s="30"/>
-      <c r="N89" s="20"/>
+      <c r="M89" s="29"/>
+      <c r="N89" s="29"/>
       <c r="O89" s="20"/>
       <c r="P89" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q89" s="20"/>
       <c r="R89"/>
@@ -5828,36 +6019,36 @@
         <v>42</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="E90" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="G90" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="H90" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I90" s="30"/>
+        <v>243</v>
+      </c>
+      <c r="F90" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="G90" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="H90" s="24">
+        <v>118.3</v>
+      </c>
+      <c r="I90" s="29"/>
       <c r="J90" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K90" s="30"/>
-      <c r="L90" s="30"/>
-      <c r="M90" s="30"/>
+        <v>125</v>
+      </c>
+      <c r="K90" s="29"/>
+      <c r="L90" s="29"/>
+      <c r="M90" s="29"/>
       <c r="N90" s="20"/>
       <c r="O90" s="20"/>
       <c r="P90" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q90" s="20"/>
       <c r="R90"/>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" s="37" customFormat="1">
       <c r="A91" s="22" t="s">
         <v>40</v>
       </c>
@@ -5868,74 +6059,74 @@
         <v>42</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="E91" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F91" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="G91" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="H91" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I91" s="29"/>
+      <c r="J91" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K91" s="29"/>
+      <c r="L91" s="29"/>
+      <c r="M91" s="29"/>
+      <c r="N91" s="20"/>
+      <c r="O91" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="P91" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q91" s="20"/>
+    </row>
+    <row r="92" spans="1:18" s="37" customFormat="1">
+      <c r="A92" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="E92" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="F91" s="24" t="s">
+      <c r="F92" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="G92" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="G91" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="H91" s="25">
-        <v>121.5</v>
-      </c>
-      <c r="I91" s="30"/>
-      <c r="J91" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K91" s="30"/>
-      <c r="L91" s="30"/>
-      <c r="M91" s="30"/>
-      <c r="N91" s="20"/>
-      <c r="O91" s="20"/>
-      <c r="P91" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q91" s="20"/>
-      <c r="R91"/>
-    </row>
-    <row r="92" spans="1:18">
-      <c r="A92" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B92" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C92" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D92" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E92" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F92" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G92" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H92" s="25">
-        <v>119.7</v>
-      </c>
-      <c r="I92" s="30"/>
-      <c r="J92" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="K92" s="30"/>
+      <c r="H92" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I92" s="29"/>
+      <c r="J92" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="K92" s="29"/>
       <c r="L92" s="30"/>
-      <c r="M92" s="30"/>
-      <c r="N92" s="20"/>
+      <c r="M92" s="29"/>
+      <c r="N92" s="29"/>
       <c r="O92" s="20"/>
       <c r="P92" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="20"/>
-      <c r="R92"/>
     </row>
     <row r="93" spans="1:18">
       <c r="A93" s="22" t="s">
@@ -5948,31 +6139,31 @@
         <v>42</v>
       </c>
       <c r="D93" s="22" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="E93" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F93" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G93" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H93" s="25">
-        <v>126.6</v>
-      </c>
-      <c r="I93" s="30"/>
+        <v>233</v>
+      </c>
+      <c r="F93" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="G93" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="H93" s="24">
+        <v>121.9</v>
+      </c>
+      <c r="I93" s="29"/>
       <c r="J93" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="K93" s="30"/>
-      <c r="L93" s="30"/>
-      <c r="M93" s="30"/>
+        <v>255</v>
+      </c>
+      <c r="K93" s="29"/>
+      <c r="L93" s="29"/>
+      <c r="M93" s="29"/>
       <c r="N93" s="20"/>
       <c r="O93" s="20"/>
       <c r="P93" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q93" s="20"/>
       <c r="R93"/>
@@ -5988,31 +6179,31 @@
         <v>42</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="E94" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H94" s="25">
-        <v>119.5</v>
-      </c>
-      <c r="I94" s="30"/>
-      <c r="J94" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="K94" s="30"/>
-      <c r="L94" s="31"/>
-      <c r="M94" s="30"/>
-      <c r="N94" s="30"/>
+        <v>233</v>
+      </c>
+      <c r="F94" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="G94" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="H94" s="24">
+        <v>132.5</v>
+      </c>
+      <c r="I94" s="29"/>
+      <c r="J94" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K94" s="29"/>
+      <c r="L94" s="29"/>
+      <c r="M94" s="29"/>
+      <c r="N94" s="20"/>
       <c r="O94" s="20"/>
       <c r="P94" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="20"/>
       <c r="R94"/>
@@ -6028,31 +6219,31 @@
         <v>42</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="E95" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F95" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G95" s="24" t="s">
-        <v>226</v>
+        <v>233</v>
+      </c>
+      <c r="F95" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="G95" s="33" t="s">
+        <v>234</v>
       </c>
       <c r="H95" s="21">
-        <v>133.9</v>
-      </c>
-      <c r="I95" s="30"/>
-      <c r="J95" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="K95" s="30"/>
-      <c r="L95" s="30"/>
-      <c r="M95" s="20"/>
+        <v>121.5</v>
+      </c>
+      <c r="I95" s="29"/>
+      <c r="J95" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K95" s="29"/>
+      <c r="L95" s="29"/>
+      <c r="M95" s="29"/>
       <c r="N95" s="20"/>
       <c r="O95" s="20"/>
       <c r="P95" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q95" s="20"/>
       <c r="R95"/>
@@ -6067,32 +6258,34 @@
       <c r="C96" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D96" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E96" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F96" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G96" s="24" t="s">
-        <v>226</v>
+      <c r="D96" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F96" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="G96" s="34" t="s">
+        <v>385</v>
       </c>
       <c r="H96" s="21">
-        <v>135</v>
-      </c>
-      <c r="I96" s="30"/>
-      <c r="J96" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="K96" s="30"/>
+        <v>128.5</v>
+      </c>
+      <c r="I96" s="36"/>
+      <c r="J96" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K96" s="29"/>
       <c r="L96" s="30"/>
-      <c r="M96" s="30"/>
-      <c r="N96" s="20"/>
-      <c r="O96" s="20"/>
+      <c r="M96" s="29"/>
+      <c r="N96" s="29"/>
+      <c r="O96" s="29" t="s">
+        <v>387</v>
+      </c>
       <c r="P96" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q96" s="20"/>
       <c r="R96"/>
@@ -6107,37 +6300,39 @@
       <c r="C97" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E97" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F97" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G97" s="24" t="s">
-        <v>226</v>
+      <c r="D97" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F97" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="G97" s="34" t="s">
+        <v>385</v>
       </c>
       <c r="H97" s="21">
-        <v>119.1</v>
-      </c>
-      <c r="I97" s="30"/>
-      <c r="J97" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="K97" s="30"/>
+        <v>133.1</v>
+      </c>
+      <c r="I97" s="36"/>
+      <c r="J97" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K97" s="29"/>
       <c r="L97" s="30"/>
-      <c r="M97" s="20"/>
-      <c r="N97" s="20"/>
-      <c r="O97" s="20"/>
+      <c r="M97" s="29"/>
+      <c r="N97" s="29"/>
+      <c r="O97" s="29" t="s">
+        <v>369</v>
+      </c>
       <c r="P97" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q97" s="20"/>
       <c r="R97"/>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" s="37" customFormat="1">
       <c r="A98" s="22" t="s">
         <v>40</v>
       </c>
@@ -6148,36 +6343,35 @@
         <v>42</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E98" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F98" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G98" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H98" s="21">
-        <v>128.1</v>
-      </c>
-      <c r="I98" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F98" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G98" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H98" s="24">
+        <v>118.3</v>
+      </c>
+      <c r="I98" s="29"/>
       <c r="J98" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="K98" s="30"/>
-      <c r="L98" s="30"/>
-      <c r="M98" s="30"/>
+        <v>46</v>
+      </c>
+      <c r="K98" s="29"/>
+      <c r="L98" s="29"/>
+      <c r="M98" s="29"/>
       <c r="N98" s="20"/>
-      <c r="O98" s="20"/>
+      <c r="O98" s="29"/>
       <c r="P98" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="20"/>
-      <c r="R98"/>
-    </row>
-    <row r="99" spans="1:18">
+    </row>
+    <row r="99" spans="1:18" s="37" customFormat="1">
       <c r="A99" s="22" t="s">
         <v>40</v>
       </c>
@@ -6188,34 +6382,33 @@
         <v>42</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E99" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F99" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G99" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H99" s="21">
-        <v>124.3</v>
-      </c>
-      <c r="I99" s="30"/>
-      <c r="J99" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="K99" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F99" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G99" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H99" s="24">
+        <v>121.9</v>
+      </c>
+      <c r="I99" s="29"/>
+      <c r="J99" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="K99" s="29"/>
       <c r="L99" s="30"/>
-      <c r="M99" s="30"/>
-      <c r="N99" s="20"/>
+      <c r="M99" s="29"/>
+      <c r="N99" s="29"/>
       <c r="O99" s="20"/>
       <c r="P99" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q99" s="20"/>
-      <c r="R99"/>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" s="22" t="s">
@@ -6228,31 +6421,31 @@
         <v>42</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F100" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G100" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H100" s="25">
-        <v>128.5</v>
-      </c>
-      <c r="I100" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F100" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G100" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H100" s="24">
+        <v>132.94999999999999</v>
+      </c>
+      <c r="I100" s="29"/>
       <c r="J100" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="K100" s="30"/>
-      <c r="L100" s="30"/>
-      <c r="M100" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="K100" s="29"/>
+      <c r="L100" s="29"/>
+      <c r="M100" s="29"/>
       <c r="N100" s="20"/>
-      <c r="O100" s="30"/>
+      <c r="O100" s="20"/>
       <c r="P100" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q100" s="20"/>
       <c r="R100"/>
@@ -6268,31 +6461,31 @@
         <v>42</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F101" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G101" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H101" s="25">
-        <v>133.1</v>
-      </c>
-      <c r="I101" s="30"/>
-      <c r="J101" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="K101" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F101" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G101" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H101" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I101" s="29"/>
+      <c r="J101" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K101" s="29"/>
       <c r="L101" s="30"/>
-      <c r="M101" s="30"/>
-      <c r="N101" s="20"/>
+      <c r="M101" s="29"/>
+      <c r="N101" s="29"/>
       <c r="O101" s="20"/>
       <c r="P101" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q101" s="20"/>
       <c r="R101"/>
@@ -6308,31 +6501,33 @@
         <v>42</v>
       </c>
       <c r="D102" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E102" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F102" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G102" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H102" s="25">
-        <v>128.80000000000001</v>
-      </c>
-      <c r="I102" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F102" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G102" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H102" s="24">
+        <v>119.75</v>
+      </c>
+      <c r="I102" s="29"/>
       <c r="J102" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="K102" s="30"/>
-      <c r="L102" s="31"/>
-      <c r="M102" s="30"/>
-      <c r="N102" s="30"/>
-      <c r="O102" s="20"/>
+        <v>315</v>
+      </c>
+      <c r="K102" s="29"/>
+      <c r="L102" s="30"/>
+      <c r="M102" s="29"/>
+      <c r="N102" s="29"/>
+      <c r="O102" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P102" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q102" s="20"/>
       <c r="R102"/>
@@ -6348,31 +6543,33 @@
         <v>42</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E103" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F103" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G103" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H103" s="25">
-        <v>124.75</v>
-      </c>
-      <c r="I103" s="30"/>
-      <c r="J103" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="K103" s="30"/>
-      <c r="L103" s="30"/>
-      <c r="M103" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F103" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G103" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="H103" s="21">
+        <v>126.9</v>
+      </c>
+      <c r="I103" s="29"/>
+      <c r="J103" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K103" s="29"/>
+      <c r="L103" s="29"/>
+      <c r="M103" s="29"/>
       <c r="N103" s="20"/>
-      <c r="O103" s="30"/>
+      <c r="O103" s="20" t="s">
+        <v>306</v>
+      </c>
       <c r="P103" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q103" s="20"/>
       <c r="R103"/>
@@ -6388,31 +6585,33 @@
         <v>42</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E104" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F104" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G104" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H104" s="25">
-        <v>118.1</v>
-      </c>
-      <c r="I104" s="30"/>
-      <c r="J104" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K104" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F104" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="G104" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="H104" s="21">
+        <v>135</v>
+      </c>
+      <c r="I104" s="36"/>
+      <c r="J104" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="K104" s="29"/>
       <c r="L104" s="30"/>
-      <c r="M104" s="30"/>
+      <c r="M104" s="29"/>
       <c r="N104" s="20"/>
-      <c r="O104" s="20"/>
+      <c r="O104" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P104" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q104" s="20"/>
       <c r="R104"/>
@@ -6428,36 +6627,38 @@
         <v>42</v>
       </c>
       <c r="D105" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E105" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F105" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G105" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H105" s="25">
-        <v>126.9</v>
-      </c>
-      <c r="I105" s="30"/>
-      <c r="J105" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="F105" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="G105" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="H105" s="21">
+        <v>119.1</v>
+      </c>
+      <c r="I105" s="36"/>
+      <c r="J105" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="K105" s="29"/>
+      <c r="L105" s="30"/>
+      <c r="M105" s="29"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="K105" s="30"/>
-      <c r="L105" s="30"/>
-      <c r="M105" s="30"/>
-      <c r="N105" s="20"/>
-      <c r="O105" s="20"/>
       <c r="P105" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q105" s="20"/>
       <c r="R105"/>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" s="37" customFormat="1">
       <c r="A106" s="22" t="s">
         <v>40</v>
       </c>
@@ -6468,34 +6669,35 @@
         <v>42</v>
       </c>
       <c r="D106" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E106" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F106" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G106" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H106" s="25">
-        <v>121.9</v>
-      </c>
-      <c r="I106" s="30"/>
-      <c r="J106" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="K106" s="30"/>
-      <c r="L106" s="31"/>
-      <c r="M106" s="30"/>
-      <c r="N106" s="30"/>
-      <c r="O106" s="20"/>
+        <v>245</v>
+      </c>
+      <c r="F106" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="G106" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="H106" s="21">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I106" s="36"/>
+      <c r="J106" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K106" s="29"/>
+      <c r="L106" s="30"/>
+      <c r="M106" s="29"/>
+      <c r="N106" s="20"/>
+      <c r="O106" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P106" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q106" s="20"/>
-      <c r="R106"/>
     </row>
     <row r="107" spans="1:18">
       <c r="A107" s="22" t="s">
@@ -6508,31 +6710,33 @@
         <v>42</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E107" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F107" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G107" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H107" s="25">
-        <v>127.3</v>
-      </c>
-      <c r="I107" s="30"/>
-      <c r="J107" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="K107" s="30"/>
+        <v>245</v>
+      </c>
+      <c r="F107" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="G107" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="H107" s="21">
+        <v>124.75</v>
+      </c>
+      <c r="I107" s="36"/>
+      <c r="J107" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K107" s="29"/>
       <c r="L107" s="30"/>
-      <c r="M107" s="30"/>
+      <c r="M107" s="29"/>
       <c r="N107" s="20"/>
-      <c r="O107" s="20"/>
+      <c r="O107" s="20" t="s">
+        <v>398</v>
+      </c>
       <c r="P107" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q107" s="20"/>
       <c r="R107"/>
@@ -6547,32 +6751,32 @@
       <c r="C108" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E108" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F108" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G108" s="24" t="s">
-        <v>226</v>
+      <c r="D108" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F108" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="G108" s="33" t="s">
+        <v>254</v>
       </c>
       <c r="H108" s="21">
-        <v>118.5</v>
-      </c>
-      <c r="I108" s="30"/>
+        <v>118.4</v>
+      </c>
+      <c r="I108" s="29"/>
       <c r="J108" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="K108" s="30"/>
-      <c r="L108" s="30"/>
-      <c r="M108" s="20"/>
+        <v>310</v>
+      </c>
+      <c r="K108" s="29"/>
+      <c r="L108" s="29"/>
+      <c r="M108" s="29"/>
       <c r="N108" s="20"/>
       <c r="O108" s="20"/>
       <c r="P108" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q108" s="20"/>
       <c r="R108"/>
@@ -6587,32 +6791,32 @@
       <c r="C109" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D109" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E109" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F109" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G109" s="24" t="s">
-        <v>226</v>
+      <c r="D109" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F109" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="G109" s="33" t="s">
+        <v>254</v>
       </c>
       <c r="H109" s="21">
-        <v>127.9</v>
-      </c>
-      <c r="I109" s="30"/>
+        <v>132.9</v>
+      </c>
+      <c r="I109" s="29"/>
       <c r="J109" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="K109" s="30"/>
-      <c r="L109" s="30"/>
-      <c r="M109" s="30"/>
+      <c r="K109" s="29"/>
+      <c r="L109" s="29"/>
+      <c r="M109" s="29"/>
       <c r="N109" s="20"/>
       <c r="O109" s="20"/>
       <c r="P109" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="20"/>
       <c r="R109"/>
@@ -6627,32 +6831,32 @@
       <c r="C110" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D110" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E110" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F110" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G110" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H110" s="25">
+      <c r="D110" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E110" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F110" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="G110" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="H110" s="21">
         <v>121.5</v>
       </c>
-      <c r="I110" s="30"/>
+      <c r="I110" s="29"/>
       <c r="J110" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="K110" s="30"/>
-      <c r="L110" s="30"/>
-      <c r="M110" s="30"/>
+        <v>300</v>
+      </c>
+      <c r="K110" s="29"/>
+      <c r="L110" s="29"/>
+      <c r="M110" s="29"/>
       <c r="N110" s="20"/>
       <c r="O110" s="20"/>
       <c r="P110" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q110" s="20"/>
       <c r="R110"/>
@@ -6667,32 +6871,34 @@
       <c r="C111" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D111" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E111" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F111" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G111" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H111" s="28">
-        <v>121.75</v>
-      </c>
-      <c r="I111" s="30"/>
-      <c r="J111" s="22" t="s">
+      <c r="D111" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F111" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="K111" s="30"/>
-      <c r="L111" s="31"/>
-      <c r="M111" s="30"/>
-      <c r="N111" s="30"/>
-      <c r="O111" s="20"/>
+      <c r="G111" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="H111" s="21">
+        <v>128.1</v>
+      </c>
+      <c r="I111" s="36"/>
+      <c r="J111" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="K111" s="29"/>
+      <c r="L111" s="30"/>
+      <c r="M111" s="29"/>
+      <c r="N111" s="20"/>
+      <c r="O111" s="20" t="s">
+        <v>356</v>
+      </c>
       <c r="P111" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q111" s="20"/>
       <c r="R111"/>
@@ -6707,32 +6913,34 @@
       <c r="C112" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D112" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E112" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F112" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G112" s="24" t="s">
-        <v>226</v>
+      <c r="D112" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E112" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F112" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="G112" s="34" t="s">
+        <v>377</v>
       </c>
       <c r="H112" s="21">
-        <v>126.1</v>
-      </c>
-      <c r="I112" s="30"/>
-      <c r="J112" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="K112" s="30"/>
+        <v>124.3</v>
+      </c>
+      <c r="I112" s="36"/>
+      <c r="J112" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="K112" s="29"/>
       <c r="L112" s="30"/>
-      <c r="M112" s="20"/>
+      <c r="M112" s="29"/>
       <c r="N112" s="20"/>
-      <c r="O112" s="20"/>
+      <c r="O112" s="20" t="s">
+        <v>403</v>
+      </c>
       <c r="P112" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q112" s="20"/>
       <c r="R112"/>
@@ -6747,32 +6955,32 @@
       <c r="C113" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D113" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E113" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F113" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G113" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H113" s="28">
-        <v>118.75</v>
-      </c>
-      <c r="I113" s="30"/>
+      <c r="D113" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F113" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="G113" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H113" s="21">
+        <v>118.1</v>
+      </c>
+      <c r="I113" s="29"/>
       <c r="J113" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="K113" s="30"/>
-      <c r="L113" s="30"/>
-      <c r="M113" s="30"/>
+        <v>46</v>
+      </c>
+      <c r="K113" s="29"/>
+      <c r="L113" s="29"/>
+      <c r="M113" s="29"/>
       <c r="N113" s="20"/>
       <c r="O113" s="20"/>
       <c r="P113" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q113" s="20"/>
       <c r="R113"/>
@@ -6787,32 +6995,32 @@
       <c r="C114" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D114" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E114" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F114" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G114" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H114" s="28">
-        <v>118.9</v>
-      </c>
-      <c r="I114" s="30"/>
+      <c r="D114" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F114" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="G114" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H114" s="21">
+        <v>130.9</v>
+      </c>
+      <c r="I114" s="29"/>
       <c r="J114" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="K114" s="30"/>
-      <c r="L114" s="31"/>
-      <c r="M114" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="K114" s="29"/>
+      <c r="L114" s="29"/>
+      <c r="M114" s="29"/>
       <c r="N114" s="20"/>
-      <c r="O114" s="30"/>
+      <c r="O114" s="20"/>
       <c r="P114" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q114" s="20"/>
       <c r="R114"/>
@@ -6827,57 +7035,1674 @@
       <c r="C115" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D115" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="E115" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="F115" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G115" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H115" s="28">
-        <v>126.9</v>
-      </c>
-      <c r="I115" s="30"/>
-      <c r="J115" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="K115" s="30"/>
-      <c r="L115" s="31"/>
-      <c r="M115" s="30"/>
-      <c r="N115" s="30"/>
+      <c r="D115" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F115" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="G115" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H115" s="21">
+        <v>121.5</v>
+      </c>
+      <c r="I115" s="29"/>
+      <c r="J115" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K115" s="29"/>
+      <c r="L115" s="29"/>
+      <c r="M115" s="29"/>
+      <c r="N115" s="20"/>
       <c r="O115" s="20"/>
       <c r="P115" s="20" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="Q115" s="20"/>
       <c r="R115"/>
     </row>
     <row r="116" spans="1:18">
-      <c r="A116" s="22"/>
-      <c r="B116" s="23"/>
-      <c r="C116" s="23"/>
-      <c r="D116" s="22"/>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
-      <c r="G116" s="22"/>
-      <c r="H116" s="25"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="19"/>
-      <c r="K116" s="18"/>
-      <c r="L116" s="18"/>
-      <c r="M116" s="18"/>
-      <c r="N116" s="19"/>
-      <c r="O116" s="19"/>
-      <c r="P116" s="9"/>
-      <c r="Q116" s="9"/>
+      <c r="A116" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D116" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F116" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="G116" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H116" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I116" s="29"/>
+      <c r="J116" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K116" s="29"/>
+      <c r="L116" s="29"/>
+      <c r="M116" s="29"/>
+      <c r="N116" s="20"/>
+      <c r="O116" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="P116" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q116" s="20"/>
       <c r="R116"/>
     </row>
+    <row r="117" spans="1:18">
+      <c r="A117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D117" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F117" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="G117" s="34" t="s">
+        <v>392</v>
+      </c>
+      <c r="H117" s="21">
+        <v>128.5</v>
+      </c>
+      <c r="I117" s="36"/>
+      <c r="J117" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K117" s="29"/>
+      <c r="L117" s="30"/>
+      <c r="M117" s="29"/>
+      <c r="N117" s="20"/>
+      <c r="O117" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="P117" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q117" s="20"/>
+    </row>
+    <row r="118" spans="1:18">
+      <c r="A118" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D118" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F118" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="G118" s="34" t="s">
+        <v>392</v>
+      </c>
+      <c r="H118" s="21">
+        <v>133.1</v>
+      </c>
+      <c r="I118" s="36"/>
+      <c r="J118" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K118" s="29"/>
+      <c r="L118" s="30"/>
+      <c r="M118" s="29"/>
+      <c r="N118" s="20"/>
+      <c r="O118" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P118" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q118" s="20"/>
+    </row>
+    <row r="119" spans="1:18" s="37" customFormat="1">
+      <c r="A119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D119" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E119" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F119" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="G119" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="H119" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I119" s="29"/>
+      <c r="J119" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K119" s="29"/>
+      <c r="L119" s="29"/>
+      <c r="M119" s="29"/>
+      <c r="N119" s="20"/>
+      <c r="O119" s="20"/>
+      <c r="P119" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q119" s="20"/>
+      <c r="R119" s="40"/>
+    </row>
+    <row r="120" spans="1:18" s="37" customFormat="1">
+      <c r="A120" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E120" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F120" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="G120" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="H120" s="24">
+        <v>118.5</v>
+      </c>
+      <c r="I120" s="29"/>
+      <c r="J120" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="K120" s="29"/>
+      <c r="L120" s="29"/>
+      <c r="M120" s="29"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="20"/>
+      <c r="P120" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q120" s="20"/>
+      <c r="R120" s="40"/>
+    </row>
+    <row r="121" spans="1:18">
+      <c r="A121" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E121" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F121" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="G121" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="H121" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I121" s="29"/>
+      <c r="J121" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K121" s="29"/>
+      <c r="L121" s="29"/>
+      <c r="M121" s="29"/>
+      <c r="N121" s="20"/>
+      <c r="O121" s="20"/>
+      <c r="P121" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q121" s="20"/>
+    </row>
+    <row r="122" spans="1:18">
+      <c r="A122" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D122" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E122" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F122" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="G122" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="H122" s="21">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="I122" s="36"/>
+      <c r="J122" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K122" s="29"/>
+      <c r="L122" s="30"/>
+      <c r="M122" s="29"/>
+      <c r="N122" s="20"/>
+      <c r="O122" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="P122" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q122" s="20"/>
+    </row>
+    <row r="123" spans="1:18">
+      <c r="A123" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D123" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E123" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F123" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="G123" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="H123" s="21">
+        <v>124.75</v>
+      </c>
+      <c r="I123" s="36"/>
+      <c r="J123" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="K123" s="29"/>
+      <c r="L123" s="30"/>
+      <c r="M123" s="29"/>
+      <c r="N123" s="20"/>
+      <c r="O123" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="P123" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q123" s="20"/>
+    </row>
+    <row r="124" spans="1:18">
+      <c r="A124" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E124" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="F124" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="G124" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="H124" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I124" s="29"/>
+      <c r="J124" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="K124" s="29"/>
+      <c r="L124" s="29"/>
+      <c r="M124" s="29"/>
+      <c r="N124" s="20"/>
+      <c r="O124" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="P124" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q124" s="20"/>
+    </row>
+    <row r="125" spans="1:18" s="37" customFormat="1">
+      <c r="A125" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E125" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="F125" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="G125" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="H125" s="24">
+        <v>118.3</v>
+      </c>
+      <c r="I125" s="29"/>
+      <c r="J125" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K125" s="29"/>
+      <c r="L125" s="29"/>
+      <c r="M125" s="29"/>
+      <c r="N125" s="20"/>
+      <c r="O125" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P125" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q125" s="20"/>
+      <c r="R125" s="40"/>
+    </row>
+    <row r="126" spans="1:18" s="37" customFormat="1">
+      <c r="A126" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E126" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="F126" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="G126" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="H126" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I126" s="29"/>
+      <c r="J126" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K126" s="29"/>
+      <c r="L126" s="30"/>
+      <c r="M126" s="29"/>
+      <c r="N126" s="29"/>
+      <c r="O126" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P126" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q126" s="20"/>
+      <c r="R126" s="40"/>
+    </row>
+    <row r="127" spans="1:18">
+      <c r="A127" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="E127" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F127" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="G127" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="H127" s="24">
+        <v>118.4</v>
+      </c>
+      <c r="I127" s="29"/>
+      <c r="J127" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="K127" s="29"/>
+      <c r="L127" s="30"/>
+      <c r="M127" s="29"/>
+      <c r="N127" s="29"/>
+      <c r="O127" s="20"/>
+      <c r="P127" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q127" s="20"/>
+    </row>
+    <row r="128" spans="1:18">
+      <c r="A128" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="E128" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F128" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="G128" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="H128" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I128" s="29"/>
+      <c r="J128" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K128" s="29"/>
+      <c r="L128" s="29"/>
+      <c r="M128" s="29"/>
+      <c r="N128" s="20"/>
+      <c r="O128" s="20"/>
+      <c r="P128" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q128" s="20"/>
+    </row>
+    <row r="129" spans="1:17">
+      <c r="A129" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B129" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C129" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="E129" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F129" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="G129" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="H129" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I129" s="29"/>
+      <c r="J129" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K129" s="29"/>
+      <c r="L129" s="29"/>
+      <c r="M129" s="29"/>
+      <c r="N129" s="20"/>
+      <c r="O129" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P129" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q129" s="20"/>
+    </row>
+    <row r="130" spans="1:17">
+      <c r="A130" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B130" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C130" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D130" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="E130" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="F130" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="G130" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="H130" s="24">
+        <v>119.5</v>
+      </c>
+      <c r="I130" s="29"/>
+      <c r="J130" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="K130" s="29"/>
+      <c r="L130" s="30"/>
+      <c r="M130" s="29"/>
+      <c r="N130" s="29"/>
+      <c r="O130" s="20"/>
+      <c r="P130" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q130" s="20"/>
+    </row>
+    <row r="131" spans="1:17">
+      <c r="A131" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B131" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D131" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="E131" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="G131" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="H131" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I131" s="29"/>
+      <c r="J131" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K131" s="29"/>
+      <c r="L131" s="29"/>
+      <c r="M131" s="29"/>
+      <c r="N131" s="20"/>
+      <c r="O131" s="20"/>
+      <c r="P131" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q131" s="20"/>
+    </row>
+    <row r="132" spans="1:17">
+      <c r="A132" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B132" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C132" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="E132" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="F132" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="G132" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="H132" s="21">
+        <v>128.1</v>
+      </c>
+      <c r="I132" s="36"/>
+      <c r="J132" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="K132" s="29"/>
+      <c r="L132" s="30"/>
+      <c r="M132" s="29"/>
+      <c r="N132" s="20"/>
+      <c r="O132" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="P132" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q132" s="20"/>
+    </row>
+    <row r="133" spans="1:17">
+      <c r="A133" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B133" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C133" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D133" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E133" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F133" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="G133" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="H133" s="24">
+        <v>118.4</v>
+      </c>
+      <c r="I133" s="29"/>
+      <c r="J133" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="K133" s="29"/>
+      <c r="L133" s="29"/>
+      <c r="M133" s="20"/>
+      <c r="N133" s="20"/>
+      <c r="O133" s="20"/>
+      <c r="P133" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q133" s="20"/>
+    </row>
+    <row r="134" spans="1:17">
+      <c r="A134" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B134" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C134" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E134" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F134" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="G134" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="H134" s="24">
+        <v>130.85</v>
+      </c>
+      <c r="I134" s="29"/>
+      <c r="J134" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K134" s="29"/>
+      <c r="L134" s="29"/>
+      <c r="M134" s="20"/>
+      <c r="N134" s="20"/>
+      <c r="O134" s="20"/>
+      <c r="P134" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q134" s="20"/>
+    </row>
+    <row r="135" spans="1:17">
+      <c r="A135" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B135" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C135" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E135" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F135" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="G135" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="H135" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I135" s="29"/>
+      <c r="J135" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K135" s="29"/>
+      <c r="L135" s="29"/>
+      <c r="M135" s="20"/>
+      <c r="N135" s="20"/>
+      <c r="O135" s="20"/>
+      <c r="P135" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q135" s="20"/>
+    </row>
+    <row r="136" spans="1:17">
+      <c r="A136" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B136" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C136" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D136" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E136" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F136" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="G136" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="H136" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I136" s="29"/>
+      <c r="J136" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K136" s="29"/>
+      <c r="L136" s="30"/>
+      <c r="M136" s="29"/>
+      <c r="N136" s="29"/>
+      <c r="O136" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P136" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q136" s="20"/>
+    </row>
+    <row r="137" spans="1:17">
+      <c r="A137" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B137" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C137" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D137" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="E137" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F137" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="G137" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="H137" s="24">
+        <v>118.7</v>
+      </c>
+      <c r="I137" s="29"/>
+      <c r="J137" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="K137" s="29"/>
+      <c r="L137" s="30"/>
+      <c r="M137" s="29"/>
+      <c r="N137" s="29"/>
+      <c r="O137" s="20"/>
+      <c r="P137" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q137" s="20"/>
+    </row>
+    <row r="138" spans="1:17">
+      <c r="A138" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B138" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="E138" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F138" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="G138" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="H138" s="24">
+        <v>126.9</v>
+      </c>
+      <c r="I138" s="29"/>
+      <c r="J138" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K138" s="29"/>
+      <c r="L138" s="30"/>
+      <c r="M138" s="29"/>
+      <c r="N138" s="29"/>
+      <c r="O138" s="20"/>
+      <c r="P138" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q138" s="20"/>
+    </row>
+    <row r="139" spans="1:17">
+      <c r="A139" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B139" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C139" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D139" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="E139" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F139" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="G139" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="H139" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I139" s="29"/>
+      <c r="J139" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K139" s="29"/>
+      <c r="L139" s="30"/>
+      <c r="M139" s="29"/>
+      <c r="N139" s="29"/>
+      <c r="O139" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P139" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q139" s="20"/>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B140" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C140" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D140" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E140" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F140" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="G140" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="H140" s="24">
+        <v>118.7</v>
+      </c>
+      <c r="I140" s="29"/>
+      <c r="J140" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="K140" s="29"/>
+      <c r="L140" s="30"/>
+      <c r="M140" s="29"/>
+      <c r="N140" s="29"/>
+      <c r="O140" s="20"/>
+      <c r="P140" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q140" s="20"/>
+    </row>
+    <row r="141" spans="1:17">
+      <c r="A141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B141" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C141" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F141" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="G141" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="H141" s="24">
+        <v>132.75</v>
+      </c>
+      <c r="I141" s="29"/>
+      <c r="J141" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K141" s="29"/>
+      <c r="L141" s="29"/>
+      <c r="M141" s="29"/>
+      <c r="N141" s="20"/>
+      <c r="O141" s="20"/>
+      <c r="P141" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q141" s="20"/>
+    </row>
+    <row r="142" spans="1:17">
+      <c r="A142" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B142" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C142" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E142" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="G142" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="H142" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I142" s="29"/>
+      <c r="J142" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K142" s="29"/>
+      <c r="L142" s="30"/>
+      <c r="M142" s="29"/>
+      <c r="N142" s="29"/>
+      <c r="O142" s="20"/>
+      <c r="P142" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q142" s="20"/>
+    </row>
+    <row r="143" spans="1:17">
+      <c r="A143" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C143" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E143" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="F143" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G143" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="H143" s="21">
+        <v>119.5</v>
+      </c>
+      <c r="I143" s="36"/>
+      <c r="J143" s="39" t="s">
+        <v>412</v>
+      </c>
+      <c r="K143" s="29"/>
+      <c r="L143" s="30"/>
+      <c r="M143" s="29"/>
+      <c r="N143" s="29"/>
+      <c r="O143" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="P143" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q143" s="20"/>
+    </row>
+    <row r="144" spans="1:17">
+      <c r="A144" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B144" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C144" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E144" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="F144" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G144" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="H144" s="21">
+        <v>133.9</v>
+      </c>
+      <c r="I144" s="36"/>
+      <c r="J144" s="39" t="s">
+        <v>412</v>
+      </c>
+      <c r="K144" s="29"/>
+      <c r="L144" s="30"/>
+      <c r="M144" s="29"/>
+      <c r="N144" s="29"/>
+      <c r="O144" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="P144" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q144" s="20"/>
+    </row>
+    <row r="145" spans="1:17">
+      <c r="A145" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B145" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C145" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E145" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="F145" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G145" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="H145" s="21">
+        <v>128.1</v>
+      </c>
+      <c r="I145" s="36"/>
+      <c r="J145" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="K145" s="29"/>
+      <c r="L145" s="30"/>
+      <c r="M145" s="29"/>
+      <c r="N145" s="29"/>
+      <c r="O145" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="P145" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q145" s="20"/>
+    </row>
+    <row r="146" spans="1:17">
+      <c r="A146" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B146" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D146" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E146" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="F146" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G146" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="H146" s="21">
+        <v>124.3</v>
+      </c>
+      <c r="I146" s="36"/>
+      <c r="J146" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="K146" s="29"/>
+      <c r="L146" s="30"/>
+      <c r="M146" s="29"/>
+      <c r="N146" s="29"/>
+      <c r="O146" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="P146" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q146" s="20"/>
+    </row>
+    <row r="147" spans="1:17">
+      <c r="A147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B147" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C147" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D147" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="E147" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="F147" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="G147" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="H147" s="24">
+        <v>126.8</v>
+      </c>
+      <c r="I147" s="29"/>
+      <c r="J147" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="K147" s="29"/>
+      <c r="L147" s="29"/>
+      <c r="M147" s="29"/>
+      <c r="N147" s="20"/>
+      <c r="O147" s="29"/>
+      <c r="P147" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q147" s="20"/>
+    </row>
+    <row r="148" spans="1:17">
+      <c r="A148" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B148" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D148" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="E148" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="F148" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="G148" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="H148" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I148" s="29"/>
+      <c r="J148" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K148" s="29"/>
+      <c r="L148" s="29"/>
+      <c r="M148" s="29"/>
+      <c r="N148" s="20"/>
+      <c r="O148" s="20"/>
+      <c r="P148" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q148" s="20"/>
+    </row>
+    <row r="149" spans="1:17">
+      <c r="A149" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B149" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C149" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D149" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E149" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F149" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G149" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="H149" s="24">
+        <v>118.1</v>
+      </c>
+      <c r="I149" s="29"/>
+      <c r="J149" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="K149" s="29"/>
+      <c r="L149" s="29"/>
+      <c r="M149" s="29"/>
+      <c r="N149" s="20"/>
+      <c r="O149" s="20"/>
+      <c r="P149" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q149" s="20"/>
+    </row>
+    <row r="150" spans="1:17">
+      <c r="A150" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B150" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C150" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D150" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E150" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F150" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G150" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="H150" s="24">
+        <v>121.5</v>
+      </c>
+      <c r="I150" s="29"/>
+      <c r="J150" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="K150" s="29"/>
+      <c r="L150" s="29"/>
+      <c r="M150" s="29"/>
+      <c r="N150" s="20"/>
+      <c r="O150" s="20"/>
+      <c r="P150" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q150" s="20"/>
+    </row>
+    <row r="151" spans="1:17">
+      <c r="A151" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B151" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C151" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D151" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E151" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F151" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G151" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="H151" s="21">
+        <v>128.5</v>
+      </c>
+      <c r="I151" s="36"/>
+      <c r="J151" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K151" s="29"/>
+      <c r="L151" s="30"/>
+      <c r="M151" s="29"/>
+      <c r="N151" s="20"/>
+      <c r="O151" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="P151" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q151" s="20"/>
+    </row>
+    <row r="152" spans="1:17">
+      <c r="A152" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B152" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D152" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E152" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F152" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G152" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="H152" s="21">
+        <v>133.1</v>
+      </c>
+      <c r="I152" s="36"/>
+      <c r="J152" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K152" s="29"/>
+      <c r="L152" s="30"/>
+      <c r="M152" s="29"/>
+      <c r="N152" s="20"/>
+      <c r="O152" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="P152" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q152" s="20"/>
+    </row>
+    <row r="153" spans="1:17">
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="31"/>
+      <c r="I153" s="32"/>
+      <c r="J153" s="7"/>
+      <c r="K153" s="7"/>
+      <c r="L153" s="8"/>
+      <c r="M153" s="7"/>
+      <c r="N153" s="7"/>
+      <c r="O153" s="9"/>
+      <c r="P153" s="9"/>
+      <c r="Q153" s="9"/>
+    </row>
+    <row r="154" spans="1:17">
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="31"/>
+      <c r="I154" s="32"/>
+      <c r="J154" s="7"/>
+      <c r="K154" s="7"/>
+      <c r="L154" s="8"/>
+      <c r="M154" s="7"/>
+      <c r="N154" s="7"/>
+      <c r="O154" s="9"/>
+      <c r="P154" s="9"/>
+      <c r="Q154" s="9"/>
+    </row>
+    <row r="155" spans="1:17">
+      <c r="A155" s="7"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="31"/>
+      <c r="I155" s="32"/>
+      <c r="J155" s="7"/>
+      <c r="K155" s="7"/>
+      <c r="L155" s="8"/>
+      <c r="M155" s="7"/>
+      <c r="N155" s="7"/>
+      <c r="O155" s="9"/>
+      <c r="P155" s="9"/>
+      <c r="Q155" s="9"/>
+    </row>
+    <row r="156" spans="1:17">
+      <c r="A156" s="7"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="31"/>
+      <c r="I156" s="32"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
+      <c r="L156" s="8"/>
+      <c r="M156" s="7"/>
+      <c r="N156" s="7"/>
+      <c r="O156" s="9"/>
+      <c r="P156" s="9"/>
+      <c r="Q156" s="9"/>
+    </row>
+    <row r="157" spans="1:17">
+      <c r="A157" s="7"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="31"/>
+      <c r="I157" s="32"/>
+      <c r="J157" s="7"/>
+      <c r="K157" s="7"/>
+      <c r="L157" s="8"/>
+      <c r="M157" s="7"/>
+      <c r="N157" s="7"/>
+      <c r="O157" s="9"/>
+      <c r="P157" s="9"/>
+      <c r="Q157" s="9"/>
+    </row>
+    <row r="158" spans="1:17">
+      <c r="A158" s="7"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="31"/>
+      <c r="I158" s="32"/>
+      <c r="J158" s="7"/>
+      <c r="K158" s="7"/>
+      <c r="L158" s="8"/>
+      <c r="M158" s="7"/>
+      <c r="N158" s="7"/>
+      <c r="O158" s="9"/>
+      <c r="P158" s="9"/>
+      <c r="Q158" s="9"/>
+    </row>
+    <row r="159" spans="1:17">
+      <c r="A159" s="7"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="31"/>
+      <c r="I159" s="32"/>
+      <c r="J159" s="7"/>
+      <c r="K159" s="7"/>
+      <c r="L159" s="8"/>
+      <c r="M159" s="7"/>
+      <c r="N159" s="7"/>
+      <c r="O159" s="9"/>
+      <c r="P159" s="9"/>
+      <c r="Q159" s="9"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="22"/>
+      <c r="B160" s="23"/>
+      <c r="C160" s="23"/>
+      <c r="D160" s="22"/>
+      <c r="E160" s="22"/>
+      <c r="F160" s="22"/>
+      <c r="G160" s="22"/>
+      <c r="H160" s="24"/>
+      <c r="I160" s="18"/>
+      <c r="J160" s="19"/>
+      <c r="K160" s="18"/>
+      <c r="L160" s="18"/>
+      <c r="M160" s="18"/>
+      <c r="N160" s="19"/>
+      <c r="O160" s="19"/>
+      <c r="P160" s="9"/>
+      <c r="Q160" s="9"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -12330,12 +14155,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100327C040EEEBC2E4E8BDF331719AF9204" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="88684b88e321fea21b9e4a93084ec042">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9000a423-ea40-4f42-aeb8-dc93288fd0d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a739dd0f12bf8c866a14a43425124bd7" ns2:_="">
     <xsd:import namespace="9000a423-ea40-4f42-aeb8-dc93288fd0d5"/>
@@ -12473,16 +14307,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36975E2A-5967-48B4-86CF-9A6B4BC252AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12491,7 +14324,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE1F23C-6AAB-4AF9-BACE-76F8046E6C50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12509,14 +14342,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" enabled="0" method="" siteId="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" removed="1"/>

--- a/Perú V.1.xlsx
+++ b/Perú V.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CELSO HOJAS DE RUTA\FRECUENCIAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07A5CBE-3FBD-44B6-9F93-E6E680E70EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895B2B52-5F89-4D93-8440-4D9DE2F5A5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="597" xr2:uid="{461DCE75-370B-4E44-A060-84CF19771C02}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="417">
   <si>
     <t>Country</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>VHF - AA/ALTERNA DE 119.500 MHz</t>
   </si>
   <si>
-    <t>VHF -  AA/ALTERNA DE 135.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">  07° 8'35.91"S</t>
   </si>
   <si>
@@ -1229,9 +1226,6 @@
     <t xml:space="preserve"> 010°41'46.53"S</t>
   </si>
   <si>
-    <t>VHF -  AA MAIN</t>
-  </si>
-  <si>
     <t>VHF - AA/ ALTERNA DE 128.500</t>
   </si>
   <si>
@@ -1320,6 +1314,9 @@
   </si>
   <si>
     <t xml:space="preserve">AREQUIPA / SIHUAS </t>
+  </si>
+  <si>
+    <t>VHF - AA/ALTERNA DE 135.00</t>
   </si>
 </sst>
 </file>
@@ -2475,23 +2472,23 @@
         <v>42</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>235</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H2" s="45">
         <v>128.80000000000001</v>
       </c>
       <c r="I2" s="43"/>
       <c r="J2" s="38" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K2" s="38"/>
       <c r="L2" s="44"/>
@@ -2515,30 +2512,30 @@
         <v>42</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>235</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H3" s="45">
         <v>124.75</v>
       </c>
       <c r="I3" s="43"/>
       <c r="J3" s="38" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K3" s="38"/>
       <c r="L3" s="44"/>
       <c r="M3" s="38"/>
       <c r="N3" s="41"/>
       <c r="O3" s="41" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
@@ -2755,23 +2752,23 @@
         <v>42</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H9" s="21">
         <v>128.80000000000001</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K9" s="29"/>
       <c r="L9" s="30"/>
@@ -2796,30 +2793,30 @@
         <v>42</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H10" s="21">
         <v>124.75</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K10" s="29"/>
       <c r="L10" s="30"/>
       <c r="M10" s="29"/>
       <c r="N10" s="20"/>
       <c r="O10" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P10" s="20" t="s">
         <v>299</v>
@@ -2837,23 +2834,23 @@
         <v>42</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H11" s="21">
         <v>128.80000000000001</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K11" s="29"/>
       <c r="L11" s="30"/>
@@ -2878,30 +2875,30 @@
         <v>42</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H12" s="21">
         <v>124.75</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K12" s="29"/>
       <c r="L12" s="30"/>
       <c r="M12" s="29"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P12" s="20" t="s">
         <v>299</v>
@@ -2925,7 +2922,7 @@
         <v>264</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G13" s="34" t="s">
         <v>265</v>
@@ -2964,7 +2961,7 @@
         <v>264</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G14" s="34" t="s">
         <v>265</v>
@@ -3003,7 +3000,7 @@
         <v>264</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G15" s="34" t="s">
         <v>265</v>
@@ -3043,7 +3040,7 @@
         <v>264</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G16" s="34" t="s">
         <v>265</v>
@@ -3083,7 +3080,7 @@
         <v>287</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G17" s="33" t="s">
         <v>288</v>
@@ -3123,7 +3120,7 @@
         <v>287</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G18" s="33" t="s">
         <v>288</v>
@@ -3159,23 +3156,23 @@
         <v>42</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H19" s="21">
         <v>128.5</v>
       </c>
       <c r="I19" s="36"/>
       <c r="J19" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K19" s="29"/>
       <c r="L19" s="30"/>
@@ -3201,30 +3198,30 @@
         <v>42</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H20" s="21">
         <v>133.1</v>
       </c>
       <c r="I20" s="36"/>
       <c r="J20" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K20" s="29"/>
       <c r="L20" s="30"/>
       <c r="M20" s="29"/>
       <c r="N20" s="29"/>
       <c r="O20" s="29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P20" s="20" t="s">
         <v>299</v>
@@ -3242,23 +3239,23 @@
         <v>42</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H21" s="21">
         <v>128.80000000000001</v>
       </c>
       <c r="I21" s="36"/>
       <c r="J21" s="39" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K21" s="29"/>
       <c r="L21" s="30"/>
@@ -3283,30 +3280,30 @@
         <v>42</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H22" s="21">
         <v>124.75</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="39" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K22" s="29"/>
       <c r="L22" s="30"/>
       <c r="M22" s="29"/>
       <c r="N22" s="29"/>
       <c r="O22" s="29" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P22" s="20" t="s">
         <v>299</v>
@@ -3330,7 +3327,7 @@
         <v>221</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G23" s="33" t="s">
         <v>222</v>
@@ -3369,7 +3366,7 @@
         <v>221</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G24" s="33" t="s">
         <v>222</v>
@@ -3409,7 +3406,7 @@
         <v>221</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>222</v>
@@ -3445,23 +3442,23 @@
         <v>42</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H26" s="21">
         <v>128.1</v>
       </c>
       <c r="I26" s="36"/>
       <c r="J26" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K26" s="29"/>
       <c r="L26" s="30"/>
@@ -3486,30 +3483,30 @@
         <v>42</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H27" s="21">
         <v>124.3</v>
       </c>
       <c r="I27" s="36"/>
       <c r="J27" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K27" s="29"/>
       <c r="L27" s="30"/>
       <c r="M27" s="29"/>
       <c r="N27" s="29"/>
       <c r="O27" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P27" s="20" t="s">
         <v>299</v>
@@ -3527,23 +3524,23 @@
         <v>42</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H28" s="21">
         <v>128.5</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K28" s="29"/>
       <c r="L28" s="30"/>
@@ -3568,30 +3565,30 @@
         <v>42</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H29" s="21">
         <v>133.1</v>
       </c>
       <c r="I29" s="36"/>
       <c r="J29" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K29" s="29"/>
       <c r="L29" s="30"/>
       <c r="M29" s="29"/>
       <c r="N29" s="29"/>
       <c r="O29" s="29" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P29" s="20" t="s">
         <v>299</v>
@@ -3977,7 +3974,7 @@
         <v>235</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>236</v>
@@ -4017,7 +4014,7 @@
         <v>235</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>236</v>
@@ -4057,7 +4054,7 @@
         <v>235</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G41" s="34" t="s">
         <v>236</v>
@@ -4097,7 +4094,7 @@
         <v>235</v>
       </c>
       <c r="F42" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G42" s="34" t="s">
         <v>236</v>
@@ -4137,7 +4134,7 @@
         <v>235</v>
       </c>
       <c r="F43" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G43" s="34" t="s">
         <v>236</v>
@@ -4177,7 +4174,7 @@
         <v>235</v>
       </c>
       <c r="F44" s="34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G44" s="34" t="s">
         <v>236</v>
@@ -4299,7 +4296,7 @@
         <v>279</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G47" s="33" t="s">
         <v>280</v>
@@ -4339,7 +4336,7 @@
         <v>279</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G48" s="33" t="s">
         <v>280</v>
@@ -4539,17 +4536,17 @@
         <v>256</v>
       </c>
       <c r="F53" s="34" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H53" s="21">
         <v>128.5</v>
       </c>
       <c r="I53" s="36"/>
       <c r="J53" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K53" s="29"/>
       <c r="L53" s="30"/>
@@ -4580,24 +4577,24 @@
         <v>256</v>
       </c>
       <c r="F54" s="34" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H54" s="21">
         <v>133.1</v>
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K54" s="29"/>
       <c r="L54" s="30"/>
       <c r="M54" s="29"/>
       <c r="N54" s="20"/>
       <c r="O54" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P54" s="20" t="s">
         <v>299</v>
@@ -4701,7 +4698,7 @@
         <v>293</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G57" s="33" t="s">
         <v>294</v>
@@ -4741,7 +4738,7 @@
         <v>293</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G58" s="33" t="s">
         <v>294</v>
@@ -4907,7 +4904,7 @@
         <v>228</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G62" s="33" t="s">
         <v>229</v>
@@ -4947,7 +4944,7 @@
         <v>228</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G63" s="33" t="s">
         <v>229</v>
@@ -4987,7 +4984,7 @@
         <v>228</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G64" s="33" t="s">
         <v>229</v>
@@ -4997,7 +4994,7 @@
       </c>
       <c r="I64" s="36"/>
       <c r="J64" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K64" s="29"/>
       <c r="L64" s="30"/>
@@ -5028,7 +5025,7 @@
         <v>228</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G65" s="33" t="s">
         <v>229</v>
@@ -5038,14 +5035,14 @@
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K65" s="29"/>
       <c r="L65" s="30"/>
       <c r="M65" s="29"/>
       <c r="N65" s="20"/>
       <c r="O65" s="20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P65" s="20" t="s">
         <v>299</v>
@@ -5069,7 +5066,7 @@
         <v>223</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G66" s="33" t="s">
         <v>224</v>
@@ -5109,7 +5106,7 @@
         <v>223</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G67" s="33" t="s">
         <v>224</v>
@@ -5149,7 +5146,7 @@
         <v>223</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G68" s="33" t="s">
         <v>224</v>
@@ -5189,7 +5186,7 @@
         <v>223</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G69" s="33" t="s">
         <v>224</v>
@@ -5229,7 +5226,7 @@
         <v>223</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G70" s="33" t="s">
         <v>224</v>
@@ -5269,7 +5266,7 @@
         <v>223</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G71" s="33" t="s">
         <v>224</v>
@@ -5309,7 +5306,7 @@
         <v>223</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G72" s="33" t="s">
         <v>224</v>
@@ -5349,7 +5346,7 @@
         <v>223</v>
       </c>
       <c r="F73" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G73" s="33" t="s">
         <v>224</v>
@@ -5389,7 +5386,7 @@
         <v>223</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G74" s="33" t="s">
         <v>224</v>
@@ -5429,7 +5426,7 @@
         <v>223</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G75" s="33" t="s">
         <v>224</v>
@@ -5469,7 +5466,7 @@
         <v>223</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G76" s="33" t="s">
         <v>224</v>
@@ -5509,7 +5506,7 @@
         <v>223</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G77" s="33" t="s">
         <v>224</v>
@@ -5549,7 +5546,7 @@
         <v>223</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G78" s="33" t="s">
         <v>224</v>
@@ -5589,7 +5586,7 @@
         <v>223</v>
       </c>
       <c r="F79" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G79" s="33" t="s">
         <v>224</v>
@@ -5629,7 +5626,7 @@
         <v>223</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G80" s="33" t="s">
         <v>224</v>
@@ -5668,7 +5665,7 @@
         <v>223</v>
       </c>
       <c r="F81" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G81" s="33" t="s">
         <v>224</v>
@@ -5707,7 +5704,7 @@
         <v>223</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G82" s="33" t="s">
         <v>224</v>
@@ -5747,7 +5744,7 @@
         <v>223</v>
       </c>
       <c r="F83" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G83" s="33" t="s">
         <v>224</v>
@@ -5787,7 +5784,7 @@
         <v>223</v>
       </c>
       <c r="F84" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G84" s="33" t="s">
         <v>224</v>
@@ -5827,7 +5824,7 @@
         <v>223</v>
       </c>
       <c r="F85" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G85" s="33" t="s">
         <v>224</v>
@@ -5866,7 +5863,7 @@
         <v>223</v>
       </c>
       <c r="F86" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G86" s="33" t="s">
         <v>224</v>
@@ -5905,7 +5902,7 @@
         <v>223</v>
       </c>
       <c r="F87" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G87" s="33" t="s">
         <v>224</v>
@@ -5945,7 +5942,7 @@
         <v>223</v>
       </c>
       <c r="F88" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G88" s="33" t="s">
         <v>224</v>
@@ -5985,7 +5982,7 @@
         <v>223</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G89" s="33" t="s">
         <v>224</v>
@@ -6025,7 +6022,7 @@
         <v>243</v>
       </c>
       <c r="F90" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G90" s="33" t="s">
         <v>244</v>
@@ -6065,7 +6062,7 @@
         <v>243</v>
       </c>
       <c r="F91" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G91" s="33" t="s">
         <v>244</v>
@@ -6106,7 +6103,7 @@
         <v>233</v>
       </c>
       <c r="F92" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G92" s="33" t="s">
         <v>234</v>
@@ -6145,7 +6142,7 @@
         <v>233</v>
       </c>
       <c r="F93" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G93" s="33" t="s">
         <v>234</v>
@@ -6185,7 +6182,7 @@
         <v>233</v>
       </c>
       <c r="F94" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G94" s="33" t="s">
         <v>234</v>
@@ -6225,7 +6222,7 @@
         <v>233</v>
       </c>
       <c r="F95" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G95" s="33" t="s">
         <v>234</v>
@@ -6259,30 +6256,30 @@
         <v>42</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F96" s="34" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H96" s="21">
         <v>128.5</v>
       </c>
       <c r="I96" s="36"/>
       <c r="J96" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K96" s="29"/>
       <c r="L96" s="30"/>
       <c r="M96" s="29"/>
       <c r="N96" s="29"/>
       <c r="O96" s="29" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="P96" s="20" t="s">
         <v>299</v>
@@ -6301,30 +6298,30 @@
         <v>42</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F97" s="34" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G97" s="34" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H97" s="21">
         <v>133.1</v>
       </c>
       <c r="I97" s="36"/>
       <c r="J97" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K97" s="29"/>
       <c r="L97" s="30"/>
       <c r="M97" s="29"/>
       <c r="N97" s="29"/>
       <c r="O97" s="29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P97" s="20" t="s">
         <v>299</v>
@@ -6349,7 +6346,7 @@
         <v>245</v>
       </c>
       <c r="F98" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G98" s="33" t="s">
         <v>246</v>
@@ -6388,7 +6385,7 @@
         <v>245</v>
       </c>
       <c r="F99" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G99" s="33" t="s">
         <v>246</v>
@@ -6427,7 +6424,7 @@
         <v>245</v>
       </c>
       <c r="F100" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G100" s="33" t="s">
         <v>246</v>
@@ -6467,7 +6464,7 @@
         <v>245</v>
       </c>
       <c r="F101" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G101" s="33" t="s">
         <v>246</v>
@@ -6507,7 +6504,7 @@
         <v>245</v>
       </c>
       <c r="F102" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G102" s="33" t="s">
         <v>246</v>
@@ -6549,7 +6546,7 @@
         <v>245</v>
       </c>
       <c r="F103" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G103" s="33" t="s">
         <v>246</v>
@@ -6591,17 +6588,17 @@
         <v>245</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G104" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H104" s="21">
         <v>135</v>
       </c>
       <c r="I104" s="36"/>
       <c r="J104" s="39" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K104" s="29"/>
       <c r="L104" s="30"/>
@@ -6633,24 +6630,24 @@
         <v>245</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G105" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H105" s="21">
         <v>119.1</v>
       </c>
       <c r="I105" s="36"/>
       <c r="J105" s="39" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K105" s="29"/>
       <c r="L105" s="30"/>
       <c r="M105" s="29"/>
       <c r="N105" s="20"/>
       <c r="O105" s="20" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="P105" s="20" t="s">
         <v>299</v>
@@ -6675,17 +6672,17 @@
         <v>245</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H106" s="21">
         <v>128.80000000000001</v>
       </c>
       <c r="I106" s="36"/>
       <c r="J106" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K106" s="29"/>
       <c r="L106" s="30"/>
@@ -6716,24 +6713,24 @@
         <v>245</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G107" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H107" s="21">
         <v>124.75</v>
       </c>
       <c r="I107" s="36"/>
       <c r="J107" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K107" s="29"/>
       <c r="L107" s="30"/>
       <c r="M107" s="29"/>
       <c r="N107" s="20"/>
       <c r="O107" s="20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P107" s="20" t="s">
         <v>299</v>
@@ -6878,17 +6875,17 @@
         <v>252</v>
       </c>
       <c r="F111" s="34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G111" s="34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H111" s="21">
         <v>128.1</v>
       </c>
       <c r="I111" s="36"/>
       <c r="J111" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K111" s="29"/>
       <c r="L111" s="30"/>
@@ -6920,24 +6917,24 @@
         <v>252</v>
       </c>
       <c r="F112" s="34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G112" s="34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H112" s="21">
         <v>124.3</v>
       </c>
       <c r="I112" s="36"/>
       <c r="J112" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K112" s="29"/>
       <c r="L112" s="30"/>
       <c r="M112" s="29"/>
       <c r="N112" s="20"/>
       <c r="O112" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P112" s="20" t="s">
         <v>299</v>
@@ -7124,17 +7121,17 @@
         <v>215</v>
       </c>
       <c r="F117" s="34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G117" s="34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H117" s="21">
         <v>128.5</v>
       </c>
       <c r="I117" s="36"/>
       <c r="J117" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K117" s="29"/>
       <c r="L117" s="30"/>
@@ -7165,24 +7162,24 @@
         <v>215</v>
       </c>
       <c r="F118" s="34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G118" s="34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H118" s="21">
         <v>133.1</v>
       </c>
       <c r="I118" s="36"/>
       <c r="J118" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K118" s="29"/>
       <c r="L118" s="30"/>
       <c r="M118" s="29"/>
       <c r="N118" s="20"/>
       <c r="O118" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P118" s="20" t="s">
         <v>299</v>
@@ -7206,7 +7203,7 @@
         <v>259</v>
       </c>
       <c r="F119" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G119" s="33" t="s">
         <v>260</v>
@@ -7246,7 +7243,7 @@
         <v>259</v>
       </c>
       <c r="F120" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G120" s="33" t="s">
         <v>260</v>
@@ -7286,7 +7283,7 @@
         <v>259</v>
       </c>
       <c r="F121" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G121" s="33" t="s">
         <v>260</v>
@@ -7325,17 +7322,17 @@
         <v>259</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G122" s="34" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H122" s="21">
         <v>128.80000000000001</v>
       </c>
       <c r="I122" s="36"/>
       <c r="J122" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K122" s="29"/>
       <c r="L122" s="30"/>
@@ -7366,24 +7363,24 @@
         <v>259</v>
       </c>
       <c r="F123" s="34" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G123" s="34" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H123" s="21">
         <v>124.75</v>
       </c>
       <c r="I123" s="36"/>
       <c r="J123" s="39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K123" s="29"/>
       <c r="L123" s="30"/>
       <c r="M123" s="29"/>
       <c r="N123" s="20"/>
       <c r="O123" s="20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P123" s="20" t="s">
         <v>299</v>
@@ -7532,7 +7529,7 @@
         <v>250</v>
       </c>
       <c r="F127" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G127" s="33" t="s">
         <v>251</v>
@@ -7571,7 +7568,7 @@
         <v>250</v>
       </c>
       <c r="F128" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G128" s="33" t="s">
         <v>251</v>
@@ -7610,7 +7607,7 @@
         <v>250</v>
       </c>
       <c r="F129" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G129" s="33" t="s">
         <v>251</v>
@@ -7739,7 +7736,7 @@
       </c>
       <c r="I132" s="36"/>
       <c r="J132" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K132" s="29"/>
       <c r="L132" s="30"/>
@@ -8174,7 +8171,7 @@
       </c>
       <c r="I143" s="36"/>
       <c r="J143" s="39" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K143" s="29"/>
       <c r="L143" s="30"/>
@@ -8215,7 +8212,7 @@
       </c>
       <c r="I144" s="36"/>
       <c r="J144" s="39" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K144" s="29"/>
       <c r="L144" s="30"/>
@@ -8256,7 +8253,7 @@
       </c>
       <c r="I145" s="36"/>
       <c r="J145" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K145" s="29"/>
       <c r="L145" s="30"/>
@@ -8297,14 +8294,14 @@
       </c>
       <c r="I146" s="36"/>
       <c r="J146" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K146" s="29"/>
       <c r="L146" s="30"/>
       <c r="M146" s="29"/>
       <c r="N146" s="29"/>
       <c r="O146" s="29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P146" s="20" t="s">
         <v>299</v>
@@ -8494,7 +8491,7 @@
       </c>
       <c r="I151" s="36"/>
       <c r="J151" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K151" s="29"/>
       <c r="L151" s="30"/>
@@ -8535,14 +8532,14 @@
       </c>
       <c r="I152" s="36"/>
       <c r="J152" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K152" s="29"/>
       <c r="L152" s="30"/>
       <c r="M152" s="29"/>
       <c r="N152" s="20"/>
       <c r="O152" s="29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P152" s="20" t="s">
         <v>299</v>
@@ -14155,21 +14152,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100327C040EEEBC2E4E8BDF331719AF9204" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="88684b88e321fea21b9e4a93084ec042">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9000a423-ea40-4f42-aeb8-dc93288fd0d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a739dd0f12bf8c866a14a43425124bd7" ns2:_="">
     <xsd:import namespace="9000a423-ea40-4f42-aeb8-dc93288fd0d5"/>
@@ -14307,24 +14289,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36975E2A-5967-48B4-86CF-9A6B4BC252AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE1F23C-6AAB-4AF9-BACE-76F8046E6C50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14342,6 +14322,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36975E2A-5967-48B4-86CF-9A6B4BC252AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" enabled="0" method="" siteId="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" removed="1"/>

--- a/Perú V.1.xlsx
+++ b/Perú V.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CELSO HOJAS DE RUTA\FRECUENCIAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895B2B52-5F89-4D93-8440-4D9DE2F5A5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92337CFD-1DBD-4ACD-AC92-C3D33A94BFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="597" xr2:uid="{461DCE75-370B-4E44-A060-84CF19771C02}"/>
   </bookViews>
@@ -14152,6 +14152,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100327C040EEEBC2E4E8BDF331719AF9204" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="88684b88e321fea21b9e4a93084ec042">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9000a423-ea40-4f42-aeb8-dc93288fd0d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a739dd0f12bf8c866a14a43425124bd7" ns2:_="">
     <xsd:import namespace="9000a423-ea40-4f42-aeb8-dc93288fd0d5"/>
@@ -14289,22 +14304,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36975E2A-5967-48B4-86CF-9A6B4BC252AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE1F23C-6AAB-4AF9-BACE-76F8046E6C50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14322,23 +14339,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36975E2A-5967-48B4-86CF-9A6B4BC252AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F564F-6E3D-4EAB-9E28-3E787BE4233A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" enabled="0" method="" siteId="{e6093642-fb63-48bb-8683-d1d5da2a12ea}" removed="1"/>
